--- a/reports/pdf_rolling5_20261030.xlsx
+++ b/reports/pdf_rolling5_20261030.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,566억   ·   현금 4억(0.1%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 8종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,493억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 8종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>289</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>6104399184</v>
+        <v>6104402746</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-174</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1546225800</v>
+        <v>-1546226702</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>179</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1526604251</v>
+        <v>1526605141</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-65</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1883380477</v>
+        <v>-1883381576</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>170</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3996374829</v>
+        <v>3996377161</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-48</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2943828801</v>
+        <v>-2943830518</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>778102777</v>
+        <v>778103231</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-47</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2144355035</v>
+        <v>-2144356286</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>35</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2981501380</v>
+        <v>2981503120</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-36</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-844501941</v>
+        <v>-844502434</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>758123388</v>
+        <v>758123831</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-15</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-626219660</v>
+        <v>-626220025</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1071531418</v>
+        <v>1071532043</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-11</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1817229813</v>
+        <v>-1817230873</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1245282523</v>
+        <v>1245283250</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-8</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2071494875</v>
+        <v>-2071496083</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>-4</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-846887540</v>
+        <v>-846888034</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>-4</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-884659519</v>
+        <v>-884660036</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,983억   ·   현금 74억(2.5%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 9종목  /  매도 15종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,943억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 9종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1167,7 +1167,7 @@
         <v>141</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2771242097</v>
+        <v>2771241374</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>-118</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1435239847</v>
+        <v>-1435239472</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>104</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>4171845445</v>
+        <v>4171844357</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>-113</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2530397606</v>
+        <v>-2530396946</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>75</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>3133394883</v>
+        <v>3133394066</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>-58</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1177318756</v>
+        <v>-1177318449</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>65</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1431104947</v>
+        <v>1431104574</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>-46</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-5496194795</v>
+        <v>-5496193362</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>4798363321</v>
+        <v>4798362070</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>-43</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-5080019811</v>
+        <v>-5080018486</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>921491966</v>
+        <v>921491725</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>-38</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1969178927</v>
+        <v>-1969178413</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>9</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>914886866</v>
+        <v>914886627</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>-33</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1134143958</v>
+        <v>-1134143662</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>147245395</v>
+        <v>147245356</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>-32</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-3149827083</v>
+        <v>-3149826262</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>2934167891</v>
+        <v>2934167126</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>-26</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-173128794</v>
+        <v>-173128748</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>-25</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-263264240</v>
+        <v>-263264172</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>-24</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-470411982</v>
+        <v>-470411860</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>-22</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-874235967</v>
+        <v>-874235740</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>-18</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-136870555</v>
+        <v>-136870519</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>-6</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-25840439</v>
+        <v>-25840432</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>-4</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-60895798</v>
+        <v>-60895782</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,229억   ·   현금 36억(1.7%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 20종목  /  매도 23종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,154억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 20종목  /  매도 23종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1820,7 +1820,7 @@
         <v>500</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>9354677805</v>
+        <v>9354679768</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>-500</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2948140884</v>
+        <v>-2948141503</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>187</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2192736477</v>
+        <v>2192736938</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>-380</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-8820410645</v>
+        <v>-8820412496</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>138</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>2310355293</v>
+        <v>2310355778</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>-190</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-6083041824</v>
+        <v>-6083043101</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1945,18 +1945,18 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍  (신규)</t>
+          <t>티에프이  (신규)</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>2634650790</v>
+        <v>5716192914</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>0.00%→2.70%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1973,7 +1973,7 @@
         <v>-170</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-3265632979</v>
+        <v>-3265633665</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>100</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>4468901340</v>
+        <v>4468902278</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>-149</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-2350408655</v>
+        <v>-2350409148</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2033,18 +2033,18 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>티에프이  (신규)</t>
+          <t>한양디지텍  (신규)</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>5716191714</v>
+        <v>2634651343</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.70%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -2061,7 +2061,7 @@
         <v>-120</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-1091745927</v>
+        <v>-1091746157</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>99</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>1611205683</v>
+        <v>1611206021</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>-119</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1192976548</v>
+        <v>-1192976798</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>98</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>2441420832</v>
+        <v>2441421345</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>-118</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1096374909</v>
+        <v>-1096375139</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>70</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2110388633</v>
+        <v>2110389076</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>-101</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1075177642</v>
+        <v>-1075177868</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>69</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>4054627516</v>
+        <v>4054628367</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>-100</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1714190514</v>
+        <v>-1714190874</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>61</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>2982357994</v>
+        <v>2982358620</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>-87</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-4125863137</v>
+        <v>-4125864003</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>60</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>4178089253</v>
+        <v>4178090130</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>-75</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-3516758554</v>
+        <v>-3516759293</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>2177755653</v>
+        <v>2177756110</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>-59</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-7642354892</v>
+        <v>-7642356496</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>49</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>823611847</v>
+        <v>823612020</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>-50</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-2067700620</v>
+        <v>-2067701054</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>38</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>2445889733</v>
+        <v>2445890247</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>-40</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-4722361416</v>
+        <v>-4722362407</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>35</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>6198099358</v>
+        <v>6198100659</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>-34</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-2195231058</v>
+        <v>-2195231519</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>30</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>4402201320</v>
+        <v>4402202244</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>-28</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-2106653432</v>
+        <v>-2106653874</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>29</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>1936234881</v>
+        <v>1936235287</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2582,23 +2582,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1067200320</v>
+        <v>-1544105787</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>1.26%→0.71%</t>
+          <t>1.54%→0.73%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
         <v>27</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>732966520</v>
+        <v>732966674</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2626,23 +2626,23 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-1544105463</v>
+        <v>-1067200544</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.54%→0.73%</t>
+          <t>1.26%→0.71%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
         <v>15</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>2606303282</v>
+        <v>2606303829</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>-21</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1650025095</v>
+        <v>-1650025441</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>-20</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-1646156494</v>
+        <v>-1646156839</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2726,23 +2726,23 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-578522623</v>
+        <v>-5259297681</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.16%</t>
+          <t>3.72%→1.44%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>100→81</t>
+          <t>30→11</t>
         </is>
       </c>
     </row>
@@ -2754,30 +2754,30 @@
       <c r="E61" s="17" t="n"/>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-5259296577</v>
+        <v>-578522745</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>3.72%→1.44%</t>
+          <t>1.46%→1.16%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>30→11</t>
+          <t>100→81</t>
         </is>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,074억   ·   현금 1억(0.1%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 5종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,054억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 5종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
         <v>138</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>2249586747</v>
+        <v>2255167953</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>-254</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-3746449944</v>
+        <v>-3755744856</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>87</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>1462043990</v>
+        <v>1465671310</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>-44</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-1312168260</v>
+        <v>-1315423740</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>85</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>804992660</v>
+        <v>806989840</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>85</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>1846344867</v>
+        <v>1850925633</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>8</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>121867224</v>
+        <v>122169576</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
     <row r="72" ht="19" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 253억   ·   현금 1억(0.6%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 5종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 245억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B72" s="4" t="n"/>
@@ -3134,11 +3134,11 @@
         <v>146</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>78489600</v>
+        <v>70734058</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>7.00%→7.28%</t>
+          <t>6.52%→6.78%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
@@ -3155,11 +3155,11 @@
         <v>-75</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-45216000</v>
+        <v>-42911987</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>1.35%→1.16%</t>
+          <t>1.32%→1.14%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -3178,11 +3178,11 @@
         <v>145</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>145603200</v>
+        <v>138643157</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>3.26%→3.82%</t>
+          <t>3.21%→3.76%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
@@ -3199,11 +3199,11 @@
         <v>-67</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-105484800</v>
+        <v>-101411168</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>5.24%→4.79%</t>
+          <t>5.20%→4.76%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -3222,11 +3222,11 @@
         <v>61</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>24126720</v>
+        <v>24243832</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>0.29%→0.39%</t>
+          <t>0.30%→0.40%</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -3243,11 +3243,11 @@
         <v>-8</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-55910400</v>
+        <v>-51251184</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>1.40%→1.17%</t>
+          <t>1.32%→1.11%</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -3266,11 +3266,11 @@
         <v>6</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>38208000</v>
+        <v>36825588</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>1.83%→1.98%</t>
+          <t>1.83%→1.97%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -3287,11 +3287,11 @@
         <v>-4</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-13363200</v>
+        <v>-12287996</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>1.00%→0.94%</t>
+          <t>0.95%→0.90%</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
@@ -3310,7 +3310,7 @@
         <v>5</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>32960000</v>
+        <v>31679990</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 419억   ·   현금 3억(0.6%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 9종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 415억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B81" s="4" t="n"/>
@@ -3427,7 +3427,7 @@
         <v>54</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>459853361</v>
+        <v>459853523</v>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>-179</v>
       </c>
       <c r="I84" s="15" t="n">
-        <v>-345677761</v>
+        <v>-345677883</v>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>11</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>1712964601</v>
+        <v>1712965202</v>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>-99</v>
       </c>
       <c r="I85" s="15" t="n">
-        <v>-100219715</v>
+        <v>-100219750</v>
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>-53</v>
       </c>
       <c r="I86" s="15" t="n">
-        <v>-386688136</v>
+        <v>-386688271</v>
       </c>
       <c r="J86" s="16" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>-48</v>
       </c>
       <c r="I87" s="15" t="n">
-        <v>-404928142</v>
+        <v>-404928284</v>
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>-40</v>
       </c>
       <c r="I88" s="15" t="n">
-        <v>-107160038</v>
+        <v>-107160075</v>
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>-31</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-190482667</v>
+        <v>-190482734</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>-21</v>
       </c>
       <c r="I90" s="15" t="n">
-        <v>-432835352</v>
+        <v>-432835504</v>
       </c>
       <c r="J90" s="16" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>-17</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>-366863529</v>
+        <v>-366863657</v>
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>-12</v>
       </c>
       <c r="I92" s="15" t="n">
-        <v>-304380107</v>
+        <v>-304380214</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
     <row r="94" ht="19" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,037억   ·   현금 65억(6.3%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 1종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,025억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B94" s="4" t="n"/>
@@ -3800,7 +3800,7 @@
         <v>8</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>102434356</v>
+        <v>102581902</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>-5</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-777626664</v>
+        <v>-778746753</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>5</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>561098757</v>
+        <v>561906961</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
     <row r="100" ht="19" customHeight="1">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 913억   ·   현금 4억(0.4%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 10종목  /  매도 12종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 907억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 10종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B100" s="4" t="n"/>
@@ -3961,7 +3961,7 @@
         <v>723</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>1221724969</v>
+        <v>1228911733</v>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>-387</v>
       </c>
       <c r="I103" s="15" t="n">
-        <v>-2457255633</v>
+        <v>-2471710372</v>
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>333</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>1426571497</v>
+        <v>1434963264</v>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>-189</v>
       </c>
       <c r="I104" s="15" t="n">
-        <v>-783971723</v>
+        <v>-788583416</v>
       </c>
       <c r="J104" s="16" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>288</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>860716496</v>
+        <v>865779637</v>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>-167</v>
       </c>
       <c r="I105" s="15" t="n">
-        <v>-397459860</v>
+        <v>-399797906</v>
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>254</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>1539366457</v>
+        <v>1548421738</v>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>-163</v>
       </c>
       <c r="I106" s="15" t="n">
-        <v>-1184602082</v>
+        <v>-1191570471</v>
       </c>
       <c r="J106" s="16" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>152</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>693803755</v>
+        <v>697885037</v>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>-97</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>-432862347</v>
+        <v>-435408648</v>
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>121</v>
       </c>
       <c r="C108" s="11" t="n">
-        <v>1065525624</v>
+        <v>1071793549</v>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>-61</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-639828774</v>
+        <v>-643592549</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>66</v>
       </c>
       <c r="C109" s="11" t="n">
-        <v>463385836</v>
+        <v>466111691</v>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>-39</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>-174037439</v>
+        <v>-175061209</v>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>60</v>
       </c>
       <c r="C110" s="11" t="n">
-        <v>155549945</v>
+        <v>156464963</v>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>-20</v>
       </c>
       <c r="I110" s="15" t="n">
-        <v>-885699687</v>
+        <v>-890909792</v>
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>51</v>
       </c>
       <c r="C111" s="11" t="n">
-        <v>537539810</v>
+        <v>540701874</v>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>-8</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>-310759890</v>
+        <v>-312587927</v>
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>17</v>
       </c>
       <c r="C112" s="11" t="n">
-        <v>356625874</v>
+        <v>358723716</v>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>-7</v>
       </c>
       <c r="I112" s="15" t="n">
-        <v>-258229909</v>
+        <v>-259748939</v>
       </c>
       <c r="J112" s="16" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>-6</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>-319769887</v>
+        <v>-321650925</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>-4</v>
       </c>
       <c r="I114" s="15" t="n">
-        <v>-282199900</v>
+        <v>-283859934</v>
       </c>
       <c r="J114" s="16" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
     <row r="116" ht="19" customHeight="1">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 308억   ·   현금 2억(0.6%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 13종목  /  매도 14종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 301억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 13종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B116" s="4" t="n"/>
@@ -4546,7 +4546,7 @@
         <v>81</v>
       </c>
       <c r="C119" s="11" t="n">
-        <v>452861172</v>
+        <v>452861495</v>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>-124</v>
       </c>
       <c r="I119" s="15" t="n">
-        <v>-383699309</v>
+        <v>-383699582</v>
       </c>
       <c r="J119" s="16" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>55</v>
       </c>
       <c r="C120" s="11" t="n">
-        <v>437860946</v>
+        <v>437861258</v>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>-77</v>
       </c>
       <c r="I120" s="15" t="n">
-        <v>-327735792</v>
+        <v>-327736026</v>
       </c>
       <c r="J120" s="16" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>39</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>163204821</v>
+        <v>163204938</v>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>-70</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>-99608576</v>
+        <v>-99608647</v>
       </c>
       <c r="J121" s="16" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>38</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>239649983</v>
+        <v>239650154</v>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>-28</v>
       </c>
       <c r="I122" s="15" t="n">
-        <v>-187193396</v>
+        <v>-187193529</v>
       </c>
       <c r="J122" s="16" t="inlineStr">
         <is>
@@ -4715,23 +4715,23 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>제이에스링크</t>
+          <t>태웅  (신규)</t>
         </is>
       </c>
       <c r="B123" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>193996754</v>
+        <v>238454513</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>0.32%→1.00%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>13→37</t>
+          <t>0→24</t>
         </is>
       </c>
       <c r="G123" s="14" t="inlineStr">
@@ -4743,7 +4743,7 @@
         <v>-25</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>-326801172</v>
+        <v>-326801405</v>
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
@@ -4759,23 +4759,23 @@
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>태웅  (신규)</t>
+          <t>제이에스링크</t>
         </is>
       </c>
       <c r="B124" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>238454343</v>
+        <v>193996892</v>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>0.32%→1.00%</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>0→24</t>
+          <t>13→37</t>
         </is>
       </c>
       <c r="G124" s="14" t="inlineStr">
@@ -4787,7 +4787,7 @@
         <v>-18</v>
       </c>
       <c r="I124" s="15" t="n">
-        <v>-94421858</v>
+        <v>-94421925</v>
       </c>
       <c r="J124" s="16" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>11</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>287121932</v>
+        <v>287122136</v>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
@@ -4824,23 +4824,23 @@
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H125" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I125" s="15" t="n">
-        <v>-231128945</v>
+        <v>-411106695</v>
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>1.73%→0.72%</t>
+          <t>3.23%→1.56%</t>
         </is>
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
         <v>7</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>363659714</v>
+        <v>363659973</v>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
@@ -4868,23 +4868,23 @@
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H126" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I126" s="15" t="n">
-        <v>-411106402</v>
+        <v>-231129110</v>
       </c>
       <c r="J126" s="16" t="inlineStr">
         <is>
-          <t>3.23%→1.56%</t>
+          <t>1.73%→0.72%</t>
         </is>
       </c>
       <c r="K126" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
         <v>6</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>99776976</v>
+        <v>99777047</v>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
@@ -4912,23 +4912,23 @@
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="H127" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I127" s="15" t="n">
-        <v>-95356477</v>
+        <v>-82558139</v>
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.64%</t>
+          <t>1.13%→0.66%</t>
         </is>
       </c>
       <c r="K127" s="13" t="inlineStr">
         <is>
-          <t>30→20</t>
+          <t>34→24</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
         <v>4</v>
       </c>
       <c r="C128" s="11" t="n">
-        <v>175809558</v>
+        <v>175809684</v>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
@@ -4956,23 +4956,23 @@
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H128" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I128" s="15" t="n">
-        <v>-82558080</v>
+        <v>-95356545</v>
       </c>
       <c r="J128" s="16" t="inlineStr">
         <is>
-          <t>1.13%→0.66%</t>
+          <t>1.07%→0.64%</t>
         </is>
       </c>
       <c r="K128" s="13" t="inlineStr">
         <is>
-          <t>34→24</t>
+          <t>30→20</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
         <v>3</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>4174214</v>
+        <v>4174217</v>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>-7</v>
       </c>
       <c r="I129" s="15" t="n">
-        <v>-102555576</v>
+        <v>-102555649</v>
       </c>
       <c r="J129" s="16" t="inlineStr">
         <is>
@@ -5023,23 +5023,23 @@
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>HT로보틱스  (신규)</t>
         </is>
       </c>
       <c r="B130" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>47930839</v>
+        <v>11291225</v>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.07%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G130" s="14" t="inlineStr">
@@ -5051,7 +5051,7 @@
         <v>-6</v>
       </c>
       <c r="I130" s="15" t="n">
-        <v>-132614969</v>
+        <v>-132615063</v>
       </c>
       <c r="J130" s="16" t="inlineStr">
         <is>
@@ -5067,23 +5067,23 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (신규)</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B131" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>11291217</v>
+        <v>47930873</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>1.05%→1.07%</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G131" s="14" t="inlineStr">
@@ -5095,7 +5095,7 @@
         <v>-5</v>
       </c>
       <c r="I131" s="15" t="n">
-        <v>-86304980</v>
+        <v>-86305041</v>
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>-3</v>
       </c>
       <c r="I132" s="15" t="n">
-        <v>-121879471</v>
+        <v>-121879558</v>
       </c>
       <c r="J132" s="16" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
     <row r="134" ht="19" customHeight="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,218억   ·   현금 20억(0.5%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
+          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,113억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B134" s="4" t="n"/>
@@ -5163,7 +5163,7 @@
     <row r="137" ht="19" customHeight="1">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억   ·   현금 47억(1.4%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B137" s="4" t="n"/>
@@ -5221,7 +5221,7 @@
     <row r="144" ht="19" customHeight="1">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억   ·   현금 6억(0.7%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 2종목</t>
+          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 808억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B144" s="4" t="n"/>
@@ -5398,7 +5398,7 @@
     <row r="150" ht="19" customHeight="1">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 374억   ·   현금 3억(0.8%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 11종목  /  매도 15종목</t>
+          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 366억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 11종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B150" s="4" t="n"/>
@@ -6083,7 +6083,7 @@
     <row r="169" ht="19" customHeight="1">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억   ·   현금 -2억(-0.4%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 5종목  /  매도 1종목</t>
+          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 540억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B169" s="4" t="n"/>
@@ -6179,11 +6179,11 @@
         <v>298</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>728431350</v>
+        <v>727120000</v>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.36%</t>
+          <t>0.00%→1.34%</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
@@ -6200,11 +6200,11 @@
         <v>-275</v>
       </c>
       <c r="I172" s="15" t="n">
-        <v>-2883568095</v>
+        <v>-2871000000</v>
       </c>
       <c r="J172" s="16" t="inlineStr">
         <is>
-          <t>5.31%→0.00%</t>
+          <t>5.23%→0.00%</t>
         </is>
       </c>
       <c r="K172" s="13" t="inlineStr">
@@ -6223,11 +6223,11 @@
         <v>154</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>681172940</v>
+        <v>681450000</v>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.27%</t>
+          <t>0.00%→1.25%</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
@@ -6251,11 +6251,11 @@
         <v>146</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>459556995</v>
+        <v>453330000</v>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.84%</t>
+          <t>0.95%→1.79%</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
@@ -6279,11 +6279,11 @@
         <v>121</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>438377040</v>
+        <v>451935000</v>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.81%</t>
+          <t>1.00%→1.84%</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
@@ -6307,11 +6307,11 @@
         <v>31</v>
       </c>
       <c r="C176" s="11" t="n">
-        <v>580351120</v>
+        <v>602020000</v>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>5.96%→7.12%</t>
+          <t>6.12%→7.28%</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="184" ht="19" customHeight="1">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억   ·   현금 2억(0.5%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 2종목</t>
+          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 281억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B184" s="4" t="n"/>
@@ -6475,7 +6475,7 @@
         <v>42</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>54285000</v>
+        <v>55271980</v>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>-95</v>
       </c>
       <c r="I187" s="15" t="n">
-        <v>-134543750</v>
+        <v>-136989951</v>
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>32</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>83864000</v>
+        <v>85388770</v>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>-3</v>
       </c>
       <c r="I188" s="15" t="n">
-        <v>-72682500</v>
+        <v>-74003974</v>
       </c>
       <c r="J188" s="16" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
     <row r="190" ht="19" customHeight="1">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억   ·   현금 2억(1.0%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
+          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 157억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B190" s="4" t="n"/>
@@ -6580,7 +6580,7 @@
     <row r="193" ht="19" customHeight="1">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 89억   ·   현금 3억(3.4%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 87억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B193" s="4" t="n"/>
@@ -6604,7 +6604,7 @@
     <row r="196" ht="19" customHeight="1">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억   ·   현금 1억(1.6%)      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 58억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B196" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261030.xlsx
+++ b/reports/pdf_rolling5_20261030.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K197"/>
+  <dimension ref="A1:K196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-23 ~ 2026-10-30  (최근 5거래일)  ·  캡처 18/23  ·  대기: TIGER, RISE, RISE, DS, RISE</t>
+          <t>최근 5거래일 변화  ·  2026-10-23 ~ 2026-10-30  (최근 5거래일)  ·  캡처 17/23  ·  대기: SOL, TIGER, RISE, RISE, DS, RISE</t>
         </is>
       </c>
     </row>
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-846888034</v>
+        <v>-884660036</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.94%</t>
+          <t>1.05%→0.69%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>24→20</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1048,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-884660036</v>
+        <v>-846888034</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.69%</t>
+          <t>1.19%→0.94%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>24→20</t>
         </is>
       </c>
     </row>
@@ -1945,18 +1945,18 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>티에프이  (신규)</t>
+          <t>에이치브이엠  (신규)</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>5716192914</v>
+        <v>4468902278</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.70%</t>
+          <t>0.00%→2.11%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1989,18 +1989,18 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>에이치브이엠  (신규)</t>
+          <t>티에프이  (신규)</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>4468902278</v>
+        <v>5716192914</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.11%</t>
+          <t>0.00%→2.70%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -2726,23 +2726,23 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-5259297681</v>
+        <v>-578522745</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>3.72%→1.44%</t>
+          <t>1.46%→1.16%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>30→11</t>
+          <t>100→81</t>
         </is>
       </c>
     </row>
@@ -2754,23 +2754,23 @@
       <c r="E61" s="17" t="n"/>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-578522745</v>
+        <v>-5259297681</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.16%</t>
+          <t>3.72%→1.44%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>100→81</t>
+          <t>30→11</t>
         </is>
       </c>
     </row>
@@ -2954,23 +2954,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>806989840</v>
+        <v>1850925633</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>1.12%→1.71%</t>
+          <t>1.01%→2.23%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>285→370</t>
+          <t>125→210</t>
         </is>
       </c>
       <c r="G68" s="17" t="n"/>
@@ -2982,23 +2982,23 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>1850925633</v>
+        <v>806989840</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>1.01%→2.23%</t>
+          <t>1.12%→1.71%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>125→210</t>
+          <t>285→370</t>
         </is>
       </c>
       <c r="G69" s="17" t="n"/>
@@ -4912,23 +4912,23 @@
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H127" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I127" s="15" t="n">
-        <v>-82558139</v>
+        <v>-95356545</v>
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>1.13%→0.66%</t>
+          <t>1.07%→0.64%</t>
         </is>
       </c>
       <c r="K127" s="13" t="inlineStr">
         <is>
-          <t>34→24</t>
+          <t>30→20</t>
         </is>
       </c>
     </row>
@@ -4956,46 +4956,46 @@
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="H128" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I128" s="15" t="n">
-        <v>-95356545</v>
+        <v>-82558139</v>
       </c>
       <c r="J128" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.64%</t>
+          <t>1.13%→0.66%</t>
         </is>
       </c>
       <c r="K128" s="13" t="inlineStr">
         <is>
-          <t>30→20</t>
+          <t>34→24</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (신규)</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B129" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>4174217</v>
+        <v>47930873</v>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>1.05%→1.07%</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G129" s="14" t="inlineStr">
@@ -5023,18 +5023,18 @@
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (신규)</t>
+          <t>피엠티  (신규)</t>
         </is>
       </c>
       <c r="B130" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>11291225</v>
+        <v>4174217</v>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
@@ -5067,23 +5067,23 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>HT로보틱스  (신규)</t>
         </is>
       </c>
       <c r="B131" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>47930873</v>
+        <v>11291225</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.07%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G131" s="14" t="inlineStr">
@@ -5137,834 +5137,855 @@
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,113억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="n"/>
-      <c r="C134" s="4" t="n"/>
-      <c r="D134" s="4" t="n"/>
-      <c r="E134" s="4" t="n"/>
-      <c r="F134" s="4" t="n"/>
-      <c r="G134" s="4" t="n"/>
-      <c r="H134" s="4" t="n"/>
-      <c r="I134" s="4" t="n"/>
-      <c r="J134" s="4" t="n"/>
-      <c r="K134" s="4" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="18" t="inlineStr">
+      <c r="A134" s="18" t="inlineStr">
+        <is>
+          <t>■ SOL 코리아메가테크액티브  (신한)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B134" s="19" t="n"/>
+      <c r="C134" s="19" t="n"/>
+      <c r="D134" s="19" t="n"/>
+      <c r="E134" s="19" t="n"/>
+      <c r="F134" s="19" t="n"/>
+      <c r="G134" s="19" t="n"/>
+      <c r="H134" s="19" t="n"/>
+      <c r="I134" s="19" t="n"/>
+      <c r="J134" s="19" t="n"/>
+      <c r="K134" s="19" t="n"/>
+    </row>
+    <row r="136" ht="19" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="n"/>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="n"/>
+      <c r="J136" s="4" t="n"/>
+      <c r="K136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="19" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="n"/>
-      <c r="C137" s="4" t="n"/>
-      <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="n"/>
-      <c r="G137" s="4" t="n"/>
-      <c r="H137" s="4" t="n"/>
-      <c r="I137" s="4" t="n"/>
-      <c r="J137" s="4" t="n"/>
-      <c r="K137" s="4" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="19" customHeight="1">
-      <c r="A140" s="19" t="inlineStr">
+    <row r="139" ht="19" customHeight="1">
+      <c r="A139" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 코리아테크액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B140" s="20" t="n"/>
-      <c r="C140" s="20" t="n"/>
-      <c r="D140" s="20" t="n"/>
-      <c r="E140" s="20" t="n"/>
-      <c r="F140" s="20" t="n"/>
-      <c r="G140" s="20" t="n"/>
-      <c r="H140" s="20" t="n"/>
-      <c r="I140" s="20" t="n"/>
-      <c r="J140" s="20" t="n"/>
-      <c r="K140" s="20" t="n"/>
-    </row>
-    <row r="142" ht="19" customHeight="1">
-      <c r="A142" s="19" t="inlineStr">
+      <c r="B139" s="19" t="n"/>
+      <c r="C139" s="19" t="n"/>
+      <c r="D139" s="19" t="n"/>
+      <c r="E139" s="19" t="n"/>
+      <c r="F139" s="19" t="n"/>
+      <c r="G139" s="19" t="n"/>
+      <c r="H139" s="19" t="n"/>
+      <c r="I139" s="19" t="n"/>
+      <c r="J139" s="19" t="n"/>
+      <c r="K139" s="19" t="n"/>
+    </row>
+    <row r="141" ht="19" customHeight="1">
+      <c r="A141" s="18" t="inlineStr">
         <is>
           <t>■ RISE 비메모리반도체액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B142" s="20" t="n"/>
-      <c r="C142" s="20" t="n"/>
-      <c r="D142" s="20" t="n"/>
-      <c r="E142" s="20" t="n"/>
-      <c r="F142" s="20" t="n"/>
-      <c r="G142" s="20" t="n"/>
-      <c r="H142" s="20" t="n"/>
-      <c r="I142" s="20" t="n"/>
-      <c r="J142" s="20" t="n"/>
-      <c r="K142" s="20" t="n"/>
-    </row>
-    <row r="144" ht="19" customHeight="1">
-      <c r="A144" s="3" t="inlineStr">
+      <c r="B141" s="19" t="n"/>
+      <c r="C141" s="19" t="n"/>
+      <c r="D141" s="19" t="n"/>
+      <c r="E141" s="19" t="n"/>
+      <c r="F141" s="19" t="n"/>
+      <c r="G141" s="19" t="n"/>
+      <c r="H141" s="19" t="n"/>
+      <c r="I141" s="19" t="n"/>
+      <c r="J141" s="19" t="n"/>
+      <c r="K141" s="19" t="n"/>
+    </row>
+    <row r="143" ht="19" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 808억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B144" s="4" t="n"/>
-      <c r="C144" s="4" t="n"/>
-      <c r="D144" s="4" t="n"/>
-      <c r="E144" s="4" t="n"/>
-      <c r="F144" s="4" t="n"/>
-      <c r="G144" s="4" t="n"/>
-      <c r="H144" s="4" t="n"/>
-      <c r="I144" s="4" t="n"/>
-      <c r="J144" s="4" t="n"/>
-      <c r="K144" s="4" t="n"/>
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="n"/>
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="n"/>
+      <c r="J143" s="4" t="n"/>
+      <c r="K143" s="4" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+      <c r="E144" s="6" t="n"/>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="n"/>
+      <c r="I144" s="8" t="n"/>
+      <c r="J144" s="8" t="n"/>
+      <c r="K144" s="8" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="n"/>
-      <c r="C145" s="6" t="n"/>
-      <c r="D145" s="6" t="n"/>
-      <c r="E145" s="6" t="n"/>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="n"/>
-      <c r="I145" s="8" t="n"/>
-      <c r="J145" s="8" t="n"/>
-      <c r="K145" s="8" t="n"/>
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B146" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C146" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D146" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E146" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G146" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H146" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I146" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J146" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K146" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>767188000</v>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>4.41%→5.30%</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>209→255</t>
+        </is>
+      </c>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="I146" s="15" t="n">
+        <v>-772132500</v>
+      </c>
+      <c r="J146" s="16" t="inlineStr">
+        <is>
+          <t>3.04%→1.69%</t>
+        </is>
+      </c>
+      <c r="K146" s="13" t="inlineStr">
+        <is>
+          <t>3,349→2,134</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B147" s="11" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>767188000</v>
+        <v>881826000</v>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>4.41%→5.30%</t>
+          <t>2.98%→4.25%</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>209→255</t>
+          <t>63→85</t>
         </is>
       </c>
       <c r="G147" s="14" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="H147" s="15" t="n">
-        <v>-1215</v>
+        <v>-117</v>
       </c>
       <c r="I147" s="15" t="n">
-        <v>-772132500</v>
+        <v>-748975500</v>
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>3.04%→1.69%</t>
+          <t>1.92%→0.86%</t>
         </is>
       </c>
       <c r="K147" s="13" t="inlineStr">
         <is>
-          <t>3,349→2,134</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="10" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="B148" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C148" s="11" t="n">
-        <v>881826000</v>
-      </c>
-      <c r="D148" s="12" t="inlineStr">
-        <is>
-          <t>2.98%→4.25%</t>
-        </is>
-      </c>
-      <c r="E148" s="13" t="inlineStr">
-        <is>
-          <t>63→85</t>
-        </is>
-      </c>
-      <c r="G148" s="14" t="inlineStr">
-        <is>
-          <t>삼성에스디에스</t>
-        </is>
-      </c>
-      <c r="H148" s="15" t="n">
-        <v>-117</v>
-      </c>
-      <c r="I148" s="15" t="n">
-        <v>-748975500</v>
-      </c>
-      <c r="J148" s="16" t="inlineStr">
-        <is>
-          <t>1.92%→0.86%</t>
-        </is>
-      </c>
-      <c r="K148" s="13" t="inlineStr">
-        <is>
           <t>225→108</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="19" customHeight="1">
-      <c r="A150" s="3" t="inlineStr">
+    <row r="149" ht="19" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
         <is>
           <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 366억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 11종목  /  매도 15종목</t>
         </is>
       </c>
-      <c r="B150" s="4" t="n"/>
-      <c r="C150" s="4" t="n"/>
-      <c r="D150" s="4" t="n"/>
-      <c r="E150" s="4" t="n"/>
-      <c r="F150" s="4" t="n"/>
-      <c r="G150" s="4" t="n"/>
-      <c r="H150" s="4" t="n"/>
-      <c r="I150" s="4" t="n"/>
-      <c r="J150" s="4" t="n"/>
-      <c r="K150" s="4" t="n"/>
+      <c r="B149" s="4" t="n"/>
+      <c r="C149" s="4" t="n"/>
+      <c r="D149" s="4" t="n"/>
+      <c r="E149" s="4" t="n"/>
+      <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="n"/>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="n"/>
+      <c r="J149" s="4" t="n"/>
+      <c r="K149" s="4" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="n"/>
+      <c r="C150" s="6" t="n"/>
+      <c r="D150" s="6" t="n"/>
+      <c r="E150" s="6" t="n"/>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="n"/>
+      <c r="I150" s="8" t="n"/>
+      <c r="J150" s="8" t="n"/>
+      <c r="K150" s="8" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="n"/>
-      <c r="C151" s="6" t="n"/>
-      <c r="D151" s="6" t="n"/>
-      <c r="E151" s="6" t="n"/>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H151" s="8" t="n"/>
-      <c r="I151" s="8" t="n"/>
-      <c r="J151" s="8" t="n"/>
-      <c r="K151" s="8" t="n"/>
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K151" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D152" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E152" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H152" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I152" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J152" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K152" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스  (신규)</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="n">
+        <v>1174</v>
+      </c>
+      <c r="C152" s="11" t="n">
+        <v>577889760</v>
+      </c>
+      <c r="D152" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.59%</t>
+        </is>
+      </c>
+      <c r="E152" s="13" t="inlineStr">
+        <is>
+          <t>0→1,174</t>
+        </is>
+      </c>
+      <c r="G152" s="14" t="inlineStr">
+        <is>
+          <t>솔루엠  (편출)</t>
+        </is>
+      </c>
+      <c r="H152" s="15" t="n">
+        <v>-574</v>
+      </c>
+      <c r="I152" s="15" t="n">
+        <v>-243972960</v>
+      </c>
+      <c r="J152" s="16" t="inlineStr">
+        <is>
+          <t>0.71%→0.00%</t>
+        </is>
+      </c>
+      <c r="K152" s="13" t="inlineStr">
+        <is>
+          <t>574→0</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>샘씨엔에스  (신규)</t>
+          <t>한화비전  (신규)</t>
         </is>
       </c>
       <c r="B153" s="11" t="n">
-        <v>1174</v>
+        <v>997</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>577889760</v>
+        <v>1370675600</v>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.59%</t>
+          <t>0.00%→3.78%</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>0→1,174</t>
+          <t>0→997</t>
         </is>
       </c>
       <c r="G153" s="14" t="inlineStr">
         <is>
-          <t>솔루엠  (편출)</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H153" s="15" t="n">
-        <v>-574</v>
+        <v>-541</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>-243972960</v>
+        <v>-691506200</v>
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.00%</t>
+          <t>3.39%→1.13%</t>
         </is>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
-          <t>574→0</t>
+          <t>861→320</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>한화비전  (신규)</t>
+          <t>인텍플러스  (신규)</t>
         </is>
       </c>
       <c r="B154" s="11" t="n">
-        <v>997</v>
+        <v>324</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>1370675600</v>
+        <v>562464000</v>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.78%</t>
+          <t>0.00%→1.55%</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>0→997</t>
+          <t>0→324</t>
         </is>
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>두산퓨얼셀  (편출)</t>
         </is>
       </c>
       <c r="H154" s="15" t="n">
-        <v>-541</v>
+        <v>-513</v>
       </c>
       <c r="I154" s="15" t="n">
-        <v>-691506200</v>
+        <v>-480475800</v>
       </c>
       <c r="J154" s="16" t="inlineStr">
         <is>
-          <t>3.39%→1.13%</t>
+          <t>1.40%→0.00%</t>
         </is>
       </c>
       <c r="K154" s="13" t="inlineStr">
         <is>
-          <t>861→320</t>
+          <t>513→0</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스  (신규)</t>
+          <t>ISC  (신규)</t>
         </is>
       </c>
       <c r="B155" s="11" t="n">
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>562464000</v>
+        <v>767844000</v>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.55%</t>
+          <t>0.00%→2.12%</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>0→324</t>
+          <t>0→165</t>
         </is>
       </c>
       <c r="G155" s="14" t="inlineStr">
         <is>
-          <t>두산퓨얼셀  (편출)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="H155" s="15" t="n">
-        <v>-513</v>
+        <v>-473</v>
       </c>
       <c r="I155" s="15" t="n">
-        <v>-480475800</v>
+        <v>-750934800</v>
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>1.40%→0.00%</t>
+          <t>2.95%→0.50%</t>
         </is>
       </c>
       <c r="K155" s="13" t="inlineStr">
         <is>
-          <t>513→0</t>
+          <t>588→115</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="10" t="inlineStr">
         <is>
-          <t>ISC  (신규)</t>
+          <t>에코프로에이치엔  (신규)</t>
         </is>
       </c>
       <c r="B156" s="11" t="n">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>767844000</v>
+        <v>73038000</v>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.12%</t>
+          <t>0.00%→0.20%</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>0→165</t>
+          <t>0→111</t>
         </is>
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>현대건설  (편출)</t>
         </is>
       </c>
       <c r="H156" s="15" t="n">
-        <v>-473</v>
+        <v>-216</v>
       </c>
       <c r="I156" s="15" t="n">
-        <v>-750934800</v>
+        <v>-562464000</v>
       </c>
       <c r="J156" s="16" t="inlineStr">
         <is>
-          <t>2.95%→0.50%</t>
+          <t>1.64%→0.00%</t>
         </is>
       </c>
       <c r="K156" s="13" t="inlineStr">
         <is>
-          <t>588→115</t>
+          <t>216→0</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔  (신규)</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B157" s="11" t="n">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>73038000</v>
+        <v>163800000</v>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.20%</t>
+          <t>4.80%→5.29%</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>0→111</t>
+          <t>644→704</t>
         </is>
       </c>
       <c r="G157" s="14" t="inlineStr">
         <is>
-          <t>현대건설  (편출)</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="H157" s="15" t="n">
-        <v>-216</v>
+        <v>-191</v>
       </c>
       <c r="I157" s="15" t="n">
-        <v>-562464000</v>
+        <v>-277026400</v>
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>1.64%→0.00%</t>
+          <t>1.54%→0.84%</t>
         </is>
       </c>
       <c r="K157" s="13" t="inlineStr">
         <is>
-          <t>216→0</t>
+          <t>401→210</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="10" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B158" s="11" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>163800000</v>
+        <v>1367296000</v>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>4.80%→5.29%</t>
+          <t>5.88%→10.71%</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>644→704</t>
+          <t>59→91</t>
         </is>
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>비에이치아이  (편출)</t>
         </is>
       </c>
       <c r="H158" s="15" t="n">
-        <v>-191</v>
+        <v>-157</v>
       </c>
       <c r="I158" s="15" t="n">
-        <v>-277026400</v>
+        <v>-201776400</v>
       </c>
       <c r="J158" s="16" t="inlineStr">
         <is>
-          <t>1.54%→0.84%</t>
+          <t>0.59%→0.00%</t>
         </is>
       </c>
       <c r="K158" s="13" t="inlineStr">
         <is>
-          <t>401→210</t>
+          <t>157→0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B159" s="11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>1367296000</v>
+        <v>168565600</v>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>5.88%→10.71%</t>
+          <t>5.37%→6.32%</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>59→91</t>
+          <t>391→422</t>
         </is>
       </c>
       <c r="G159" s="14" t="inlineStr">
         <is>
-          <t>비에이치아이  (편출)</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="H159" s="15" t="n">
-        <v>-157</v>
+        <v>-138</v>
       </c>
       <c r="I159" s="15" t="n">
-        <v>-201776400</v>
+        <v>-896448000</v>
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.00%</t>
+          <t>8.52%→6.26%</t>
         </is>
       </c>
       <c r="K159" s="13" t="inlineStr">
         <is>
-          <t>157→0</t>
+          <t>488→350</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B160" s="11" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>168565600</v>
+        <v>118431600</v>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>5.37%→6.32%</t>
+          <t>5.23%→5.77%</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>391→422</t>
+          <t>384→407</t>
         </is>
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK텔레콤  (편출)</t>
         </is>
       </c>
       <c r="H160" s="15" t="n">
-        <v>-138</v>
+        <v>-77</v>
       </c>
       <c r="I160" s="15" t="n">
-        <v>-896448000</v>
+        <v>-164287200</v>
       </c>
       <c r="J160" s="16" t="inlineStr">
         <is>
-          <t>8.52%→6.26%</t>
+          <t>0.48%→0.00%</t>
         </is>
       </c>
       <c r="K160" s="13" t="inlineStr">
         <is>
-          <t>488→350</t>
+          <t>77→0</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B161" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>118431600</v>
+        <v>331408000</v>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>5.23%→5.77%</t>
+          <t>5.59%→6.47%</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>384→407</t>
+          <t>134→156</t>
         </is>
       </c>
       <c r="G161" s="14" t="inlineStr">
         <is>
-          <t>SK텔레콤  (편출)</t>
+          <t>DB하이텍  (편출)</t>
         </is>
       </c>
       <c r="H161" s="15" t="n">
-        <v>-77</v>
+        <v>-69</v>
       </c>
       <c r="I161" s="15" t="n">
-        <v>-164287200</v>
+        <v>-191074800</v>
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.00%</t>
+          <t>0.56%→0.00%</t>
         </is>
       </c>
       <c r="K161" s="13" t="inlineStr">
         <is>
-          <t>77→0</t>
+          <t>69→0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B162" s="11" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>331408000</v>
+        <v>108612000</v>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>5.59%→6.47%</t>
+          <t>1.12%→1.50%</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>134→156</t>
+          <t>12→15</t>
         </is>
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>DB하이텍  (편출)</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H162" s="15" t="n">
-        <v>-69</v>
+        <v>-43</v>
       </c>
       <c r="I162" s="15" t="n">
-        <v>-191074800</v>
+        <v>-144841200</v>
       </c>
       <c r="J162" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.00%</t>
+          <t>3.04%→2.55%</t>
         </is>
       </c>
       <c r="K162" s="13" t="inlineStr">
         <is>
-          <t>69→0</t>
+          <t>318→275</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="10" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="B163" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C163" s="11" t="n">
-        <v>108612000</v>
-      </c>
-      <c r="D163" s="12" t="inlineStr">
-        <is>
-          <t>1.12%→1.50%</t>
-        </is>
-      </c>
-      <c r="E163" s="13" t="inlineStr">
-        <is>
-          <t>12→15</t>
-        </is>
-      </c>
+      <c r="A163" s="17" t="n"/>
+      <c r="B163" s="17" t="n"/>
+      <c r="C163" s="17" t="n"/>
+      <c r="D163" s="17" t="n"/>
+      <c r="E163" s="17" t="n"/>
       <c r="G163" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="H163" s="15" t="n">
-        <v>-43</v>
+        <v>-30</v>
       </c>
       <c r="I163" s="15" t="n">
-        <v>-144841200</v>
+        <v>-299040000</v>
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>3.04%→2.55%</t>
+          <t>4.19%→2.80%</t>
         </is>
       </c>
       <c r="K163" s="13" t="inlineStr">
         <is>
-          <t>318→275</t>
+          <t>132→102</t>
         </is>
       </c>
     </row>
@@ -5976,23 +5997,23 @@
       <c r="E164" s="17" t="n"/>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="H164" s="15" t="n">
-        <v>-30</v>
+        <v>-24</v>
       </c>
       <c r="I164" s="15" t="n">
-        <v>-299040000</v>
+        <v>-18480000</v>
       </c>
       <c r="J164" s="16" t="inlineStr">
         <is>
-          <t>4.19%→2.80%</t>
+          <t>3.01%→2.77%</t>
         </is>
       </c>
       <c r="K164" s="13" t="inlineStr">
         <is>
-          <t>132→102</t>
+          <t>1,328→1,304</t>
         </is>
       </c>
     </row>
@@ -6004,23 +6025,23 @@
       <c r="E165" s="17" t="n"/>
       <c r="G165" s="14" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>두산  (편출)</t>
         </is>
       </c>
       <c r="H165" s="15" t="n">
-        <v>-24</v>
+        <v>-19</v>
       </c>
       <c r="I165" s="15" t="n">
-        <v>-18480000</v>
+        <v>-536788000</v>
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>3.01%→2.77%</t>
+          <t>1.56%→0.00%</t>
         </is>
       </c>
       <c r="K165" s="13" t="inlineStr">
         <is>
-          <t>1,328→1,304</t>
+          <t>19→0</t>
         </is>
       </c>
     </row>
@@ -6032,207 +6053,207 @@
       <c r="E166" s="17" t="n"/>
       <c r="G166" s="14" t="inlineStr">
         <is>
-          <t>두산  (편출)</t>
+          <t>HD현대일렉트릭  (편출)</t>
         </is>
       </c>
       <c r="H166" s="15" t="n">
-        <v>-19</v>
+        <v>-13</v>
       </c>
       <c r="I166" s="15" t="n">
-        <v>-536788000</v>
+        <v>-178360000</v>
       </c>
       <c r="J166" s="16" t="inlineStr">
         <is>
-          <t>1.56%→0.00%</t>
+          <t>0.52%→0.00%</t>
         </is>
       </c>
       <c r="K166" s="13" t="inlineStr">
         <is>
-          <t>19→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="17" t="n"/>
-      <c r="B167" s="17" t="n"/>
-      <c r="C167" s="17" t="n"/>
-      <c r="D167" s="17" t="n"/>
-      <c r="E167" s="17" t="n"/>
-      <c r="G167" s="14" t="inlineStr">
-        <is>
-          <t>HD현대일렉트릭  (편출)</t>
-        </is>
-      </c>
-      <c r="H167" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I167" s="15" t="n">
-        <v>-178360000</v>
-      </c>
-      <c r="J167" s="16" t="inlineStr">
-        <is>
-          <t>0.52%→0.00%</t>
-        </is>
-      </c>
-      <c r="K167" s="13" t="inlineStr">
-        <is>
           <t>13→0</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="19" customHeight="1">
-      <c r="A169" s="3" t="inlineStr">
+    <row r="168" ht="19" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 540억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
-      <c r="B169" s="4" t="n"/>
-      <c r="C169" s="4" t="n"/>
-      <c r="D169" s="4" t="n"/>
-      <c r="E169" s="4" t="n"/>
-      <c r="F169" s="4" t="n"/>
-      <c r="G169" s="4" t="n"/>
-      <c r="H169" s="4" t="n"/>
-      <c r="I169" s="4" t="n"/>
-      <c r="J169" s="4" t="n"/>
-      <c r="K169" s="4" t="n"/>
+      <c r="B168" s="4" t="n"/>
+      <c r="C168" s="4" t="n"/>
+      <c r="D168" s="4" t="n"/>
+      <c r="E168" s="4" t="n"/>
+      <c r="F168" s="4" t="n"/>
+      <c r="G168" s="4" t="n"/>
+      <c r="H168" s="4" t="n"/>
+      <c r="I168" s="4" t="n"/>
+      <c r="J168" s="4" t="n"/>
+      <c r="K168" s="4" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="n"/>
+      <c r="C169" s="6" t="n"/>
+      <c r="D169" s="6" t="n"/>
+      <c r="E169" s="6" t="n"/>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H169" s="8" t="n"/>
+      <c r="I169" s="8" t="n"/>
+      <c r="J169" s="8" t="n"/>
+      <c r="K169" s="8" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="n"/>
-      <c r="C170" s="6" t="n"/>
-      <c r="D170" s="6" t="n"/>
-      <c r="E170" s="6" t="n"/>
-      <c r="G170" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H170" s="8" t="n"/>
-      <c r="I170" s="8" t="n"/>
-      <c r="J170" s="8" t="n"/>
-      <c r="K170" s="8" t="n"/>
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E170" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K170" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B171" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C171" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D171" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E171" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G171" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H171" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I171" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J171" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K171" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A171" s="10" t="inlineStr">
+        <is>
+          <t>디케이티  (신규)</t>
+        </is>
+      </c>
+      <c r="B171" s="11" t="n">
+        <v>298</v>
+      </c>
+      <c r="C171" s="11" t="n">
+        <v>727120000</v>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.34%</t>
+        </is>
+      </c>
+      <c r="E171" s="13" t="inlineStr">
+        <is>
+          <t>0→298</t>
+        </is>
+      </c>
+      <c r="G171" s="14" t="inlineStr">
+        <is>
+          <t>기가비스  (편출)</t>
+        </is>
+      </c>
+      <c r="H171" s="15" t="n">
+        <v>-275</v>
+      </c>
+      <c r="I171" s="15" t="n">
+        <v>-2871000000</v>
+      </c>
+      <c r="J171" s="16" t="inlineStr">
+        <is>
+          <t>5.23%→0.00%</t>
+        </is>
+      </c>
+      <c r="K171" s="13" t="inlineStr">
+        <is>
+          <t>275→0</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>GST  (신규)</t>
         </is>
       </c>
       <c r="B172" s="11" t="n">
-        <v>298</v>
+        <v>154</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>727120000</v>
+        <v>681450000</v>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.34%</t>
+          <t>0.00%→1.25%</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>0→298</t>
-        </is>
-      </c>
-      <c r="G172" s="14" t="inlineStr">
-        <is>
-          <t>기가비스  (편출)</t>
-        </is>
-      </c>
-      <c r="H172" s="15" t="n">
-        <v>-275</v>
-      </c>
-      <c r="I172" s="15" t="n">
-        <v>-2871000000</v>
-      </c>
-      <c r="J172" s="16" t="inlineStr">
-        <is>
-          <t>5.23%→0.00%</t>
-        </is>
-      </c>
-      <c r="K172" s="13" t="inlineStr">
-        <is>
-          <t>275→0</t>
-        </is>
-      </c>
+          <t>0→154</t>
+        </is>
+      </c>
+      <c r="G172" s="17" t="n"/>
+      <c r="H172" s="17" t="n"/>
+      <c r="I172" s="17" t="n"/>
+      <c r="J172" s="17" t="n"/>
+      <c r="K172" s="17" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>GST  (신규)</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B173" s="11" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>681450000</v>
+        <v>453330000</v>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.25%</t>
+          <t>0.95%→1.79%</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>0→154</t>
+          <t>168→314</t>
         </is>
       </c>
       <c r="G173" s="17" t="n"/>
@@ -6244,23 +6265,23 @@
     <row r="174">
       <c r="A174" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="B174" s="11" t="n">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>453330000</v>
+        <v>451935000</v>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>0.95%→1.79%</t>
+          <t>1.00%→1.84%</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>168→314</t>
+          <t>147→268</t>
         </is>
       </c>
       <c r="G174" s="17" t="n"/>
@@ -6272,23 +6293,23 @@
     <row r="175">
       <c r="A175" s="10" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B175" s="11" t="n">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>451935000</v>
+        <v>602020000</v>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.84%</t>
+          <t>6.12%→7.28%</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>147→268</t>
+          <t>173→204</t>
         </is>
       </c>
       <c r="G175" s="17" t="n"/>
@@ -6297,392 +6318,363 @@
       <c r="J175" s="17" t="n"/>
       <c r="K175" s="17" t="n"/>
     </row>
-    <row r="176">
-      <c r="A176" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="B176" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="C176" s="11" t="n">
-        <v>602020000</v>
-      </c>
-      <c r="D176" s="12" t="inlineStr">
-        <is>
-          <t>6.12%→7.28%</t>
-        </is>
-      </c>
-      <c r="E176" s="13" t="inlineStr">
-        <is>
-          <t>173→204</t>
-        </is>
-      </c>
-      <c r="G176" s="17" t="n"/>
-      <c r="H176" s="17" t="n"/>
-      <c r="I176" s="17" t="n"/>
-      <c r="J176" s="17" t="n"/>
-      <c r="K176" s="17" t="n"/>
-    </row>
-    <row r="178" ht="19" customHeight="1">
-      <c r="A178" s="19" t="inlineStr">
+    <row r="177" ht="19" customHeight="1">
+      <c r="A177" s="18" t="inlineStr">
         <is>
           <t>■ RISE 반도체소부장액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B178" s="20" t="n"/>
-      <c r="C178" s="20" t="n"/>
-      <c r="D178" s="20" t="n"/>
-      <c r="E178" s="20" t="n"/>
-      <c r="F178" s="20" t="n"/>
-      <c r="G178" s="20" t="n"/>
-      <c r="H178" s="20" t="n"/>
-      <c r="I178" s="20" t="n"/>
-      <c r="J178" s="20" t="n"/>
-      <c r="K178" s="20" t="n"/>
-    </row>
-    <row r="180" ht="19" customHeight="1">
-      <c r="A180" s="19" t="inlineStr">
+      <c r="B177" s="19" t="n"/>
+      <c r="C177" s="19" t="n"/>
+      <c r="D177" s="19" t="n"/>
+      <c r="E177" s="19" t="n"/>
+      <c r="F177" s="19" t="n"/>
+      <c r="G177" s="19" t="n"/>
+      <c r="H177" s="19" t="n"/>
+      <c r="I177" s="19" t="n"/>
+      <c r="J177" s="19" t="n"/>
+      <c r="K177" s="19" t="n"/>
+    </row>
+    <row r="179" ht="19" customHeight="1">
+      <c r="A179" s="18" t="inlineStr">
         <is>
           <t>■ DS AI반도체액티브  (DS)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B180" s="20" t="n"/>
-      <c r="C180" s="20" t="n"/>
-      <c r="D180" s="20" t="n"/>
-      <c r="E180" s="20" t="n"/>
-      <c r="F180" s="20" t="n"/>
-      <c r="G180" s="20" t="n"/>
-      <c r="H180" s="20" t="n"/>
-      <c r="I180" s="20" t="n"/>
-      <c r="J180" s="20" t="n"/>
-      <c r="K180" s="20" t="n"/>
-    </row>
-    <row r="182" ht="19" customHeight="1">
-      <c r="A182" s="19" t="inlineStr">
+      <c r="B179" s="19" t="n"/>
+      <c r="C179" s="19" t="n"/>
+      <c r="D179" s="19" t="n"/>
+      <c r="E179" s="19" t="n"/>
+      <c r="F179" s="19" t="n"/>
+      <c r="G179" s="19" t="n"/>
+      <c r="H179" s="19" t="n"/>
+      <c r="I179" s="19" t="n"/>
+      <c r="J179" s="19" t="n"/>
+      <c r="K179" s="19" t="n"/>
+    </row>
+    <row r="181" ht="19" customHeight="1">
+      <c r="A181" s="18" t="inlineStr">
         <is>
           <t>■ RISE 2차전지액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B182" s="20" t="n"/>
-      <c r="C182" s="20" t="n"/>
-      <c r="D182" s="20" t="n"/>
-      <c r="E182" s="20" t="n"/>
-      <c r="F182" s="20" t="n"/>
-      <c r="G182" s="20" t="n"/>
-      <c r="H182" s="20" t="n"/>
-      <c r="I182" s="20" t="n"/>
-      <c r="J182" s="20" t="n"/>
-      <c r="K182" s="20" t="n"/>
-    </row>
-    <row r="184" ht="19" customHeight="1">
-      <c r="A184" s="3" t="inlineStr">
+      <c r="B181" s="19" t="n"/>
+      <c r="C181" s="19" t="n"/>
+      <c r="D181" s="19" t="n"/>
+      <c r="E181" s="19" t="n"/>
+      <c r="F181" s="19" t="n"/>
+      <c r="G181" s="19" t="n"/>
+      <c r="H181" s="19" t="n"/>
+      <c r="I181" s="19" t="n"/>
+      <c r="J181" s="19" t="n"/>
+      <c r="K181" s="19" t="n"/>
+    </row>
+    <row r="183" ht="19" customHeight="1">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 281억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B184" s="4" t="n"/>
-      <c r="C184" s="4" t="n"/>
-      <c r="D184" s="4" t="n"/>
-      <c r="E184" s="4" t="n"/>
-      <c r="F184" s="4" t="n"/>
-      <c r="G184" s="4" t="n"/>
-      <c r="H184" s="4" t="n"/>
-      <c r="I184" s="4" t="n"/>
-      <c r="J184" s="4" t="n"/>
-      <c r="K184" s="4" t="n"/>
+      <c r="B183" s="4" t="n"/>
+      <c r="C183" s="4" t="n"/>
+      <c r="D183" s="4" t="n"/>
+      <c r="E183" s="4" t="n"/>
+      <c r="F183" s="4" t="n"/>
+      <c r="G183" s="4" t="n"/>
+      <c r="H183" s="4" t="n"/>
+      <c r="I183" s="4" t="n"/>
+      <c r="J183" s="4" t="n"/>
+      <c r="K183" s="4" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="n"/>
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="6" t="n"/>
+      <c r="E184" s="6" t="n"/>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H184" s="8" t="n"/>
+      <c r="I184" s="8" t="n"/>
+      <c r="J184" s="8" t="n"/>
+      <c r="K184" s="8" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="n"/>
-      <c r="C185" s="6" t="n"/>
-      <c r="D185" s="6" t="n"/>
-      <c r="E185" s="6" t="n"/>
-      <c r="G185" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H185" s="8" t="n"/>
-      <c r="I185" s="8" t="n"/>
-      <c r="J185" s="8" t="n"/>
-      <c r="K185" s="8" t="n"/>
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E185" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I185" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K185" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B186" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C186" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D186" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E186" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G186" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H186" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I186" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J186" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K186" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A186" s="10" t="inlineStr">
+        <is>
+          <t>에코프로에이치엔</t>
+        </is>
+      </c>
+      <c r="B186" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C186" s="11" t="n">
+        <v>55271980</v>
+      </c>
+      <c r="D186" s="12" t="inlineStr">
+        <is>
+          <t>0.51%→0.73%</t>
+        </is>
+      </c>
+      <c r="E186" s="13" t="inlineStr">
+        <is>
+          <t>112→154</t>
+        </is>
+      </c>
+      <c r="G186" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H186" s="15" t="n">
+        <v>-95</v>
+      </c>
+      <c r="I186" s="15" t="n">
+        <v>-136989951</v>
+      </c>
+      <c r="J186" s="16" t="inlineStr">
+        <is>
+          <t>8.88%→9.20%</t>
+        </is>
+      </c>
+      <c r="K186" s="13" t="inlineStr">
+        <is>
+          <t>1,876→1,781</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B187" s="11" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>55271980</v>
+        <v>85388770</v>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>0.51%→0.73%</t>
+          <t>6.94%→7.49%</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>112→154</t>
+          <t>752→784</t>
         </is>
       </c>
       <c r="G187" s="14" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>HD현대일렉트릭</t>
         </is>
       </c>
       <c r="H187" s="15" t="n">
-        <v>-95</v>
+        <v>-3</v>
       </c>
       <c r="I187" s="15" t="n">
-        <v>-136989951</v>
+        <v>-74003974</v>
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
-          <t>8.88%→9.20%</t>
+          <t>2.20%→1.85%</t>
         </is>
       </c>
       <c r="K187" s="13" t="inlineStr">
         <is>
-          <t>1,876→1,781</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="10" t="inlineStr">
-        <is>
-          <t>한중엔시에스</t>
-        </is>
-      </c>
-      <c r="B188" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="C188" s="11" t="n">
-        <v>85388770</v>
-      </c>
-      <c r="D188" s="12" t="inlineStr">
-        <is>
-          <t>6.94%→7.49%</t>
-        </is>
-      </c>
-      <c r="E188" s="13" t="inlineStr">
-        <is>
-          <t>752→784</t>
-        </is>
-      </c>
-      <c r="G188" s="14" t="inlineStr">
-        <is>
-          <t>HD현대일렉트릭</t>
-        </is>
-      </c>
-      <c r="H188" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I188" s="15" t="n">
-        <v>-74003974</v>
-      </c>
-      <c r="J188" s="16" t="inlineStr">
-        <is>
-          <t>2.20%→1.85%</t>
-        </is>
-      </c>
-      <c r="K188" s="13" t="inlineStr">
-        <is>
           <t>24→21</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="19" customHeight="1">
-      <c r="A190" s="3" t="inlineStr">
+    <row r="189" ht="19" customHeight="1">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 157억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B190" s="4" t="n"/>
-      <c r="C190" s="4" t="n"/>
-      <c r="D190" s="4" t="n"/>
-      <c r="E190" s="4" t="n"/>
-      <c r="F190" s="4" t="n"/>
-      <c r="G190" s="4" t="n"/>
-      <c r="H190" s="4" t="n"/>
-      <c r="I190" s="4" t="n"/>
-      <c r="J190" s="4" t="n"/>
-      <c r="K190" s="4" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="18" t="inlineStr">
+      <c r="B189" s="4" t="n"/>
+      <c r="C189" s="4" t="n"/>
+      <c r="D189" s="4" t="n"/>
+      <c r="E189" s="4" t="n"/>
+      <c r="F189" s="4" t="n"/>
+      <c r="G189" s="4" t="n"/>
+      <c r="H189" s="4" t="n"/>
+      <c r="I189" s="4" t="n"/>
+      <c r="J189" s="4" t="n"/>
+      <c r="K189" s="4" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="19" customHeight="1">
-      <c r="A193" s="3" t="inlineStr">
+    <row r="192" ht="19" customHeight="1">
+      <c r="A192" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 87억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B193" s="4" t="n"/>
-      <c r="C193" s="4" t="n"/>
-      <c r="D193" s="4" t="n"/>
-      <c r="E193" s="4" t="n"/>
-      <c r="F193" s="4" t="n"/>
-      <c r="G193" s="4" t="n"/>
-      <c r="H193" s="4" t="n"/>
-      <c r="I193" s="4" t="n"/>
-      <c r="J193" s="4" t="n"/>
-      <c r="K193" s="4" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="18" t="inlineStr">
+      <c r="B192" s="4" t="n"/>
+      <c r="C192" s="4" t="n"/>
+      <c r="D192" s="4" t="n"/>
+      <c r="E192" s="4" t="n"/>
+      <c r="F192" s="4" t="n"/>
+      <c r="G192" s="4" t="n"/>
+      <c r="H192" s="4" t="n"/>
+      <c r="I192" s="4" t="n"/>
+      <c r="J192" s="4" t="n"/>
+      <c r="K192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="19" customHeight="1">
-      <c r="A196" s="3" t="inlineStr">
+    <row r="195" ht="19" customHeight="1">
+      <c r="A195" s="3" t="inlineStr">
         <is>
           <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 58억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B196" s="4" t="n"/>
-      <c r="C196" s="4" t="n"/>
-      <c r="D196" s="4" t="n"/>
-      <c r="E196" s="4" t="n"/>
-      <c r="F196" s="4" t="n"/>
-      <c r="G196" s="4" t="n"/>
-      <c r="H196" s="4" t="n"/>
-      <c r="I196" s="4" t="n"/>
-      <c r="J196" s="4" t="n"/>
-      <c r="K196" s="4" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="18" t="inlineStr">
+      <c r="B195" s="4" t="n"/>
+      <c r="C195" s="4" t="n"/>
+      <c r="D195" s="4" t="n"/>
+      <c r="E195" s="4" t="n"/>
+      <c r="F195" s="4" t="n"/>
+      <c r="G195" s="4" t="n"/>
+      <c r="H195" s="4" t="n"/>
+      <c r="I195" s="4" t="n"/>
+      <c r="J195" s="4" t="n"/>
+      <c r="K195" s="4" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="G185:K185"/>
+  <mergeCells count="55">
+    <mergeCell ref="A143:K143"/>
     <mergeCell ref="A73:E73"/>
     <mergeCell ref="A64:E64"/>
     <mergeCell ref="A82:E82"/>
     <mergeCell ref="G117:K117"/>
-    <mergeCell ref="A142:K142"/>
-    <mergeCell ref="A182:K182"/>
-    <mergeCell ref="G151:K151"/>
-    <mergeCell ref="A178:K178"/>
-    <mergeCell ref="A191:K191"/>
+    <mergeCell ref="A169:E169"/>
+    <mergeCell ref="G169:K169"/>
     <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A138:K138"/>
-    <mergeCell ref="G145:K145"/>
-    <mergeCell ref="A169:K169"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A94:K94"/>
-    <mergeCell ref="G170:K170"/>
-    <mergeCell ref="A197:K197"/>
+    <mergeCell ref="A168:K168"/>
     <mergeCell ref="G82:K82"/>
     <mergeCell ref="G101:K101"/>
     <mergeCell ref="A196:K196"/>
     <mergeCell ref="A137:K137"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="G37:K37"/>
+    <mergeCell ref="A177:K177"/>
+    <mergeCell ref="A183:K183"/>
+    <mergeCell ref="G184:K184"/>
     <mergeCell ref="A193:K193"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="G18:K18"/>
-    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A189:K189"/>
+    <mergeCell ref="A136:K136"/>
+    <mergeCell ref="A192:K192"/>
+    <mergeCell ref="A149:K149"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A139:K139"/>
+    <mergeCell ref="A179:K179"/>
+    <mergeCell ref="A195:K195"/>
     <mergeCell ref="G95:K95"/>
-    <mergeCell ref="A151:E151"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A185:E185"/>
-    <mergeCell ref="A194:K194"/>
     <mergeCell ref="A116:K116"/>
+    <mergeCell ref="A150:E150"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G73:K73"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A144:K144"/>
+    <mergeCell ref="A141:K141"/>
     <mergeCell ref="G64:K64"/>
-    <mergeCell ref="A150:K150"/>
-    <mergeCell ref="A135:K135"/>
-    <mergeCell ref="A184:K184"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="A181:K181"/>
+    <mergeCell ref="A184:E184"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A100:K100"/>
-    <mergeCell ref="A140:K140"/>
+    <mergeCell ref="G144:K144"/>
     <mergeCell ref="A72:K72"/>
     <mergeCell ref="A134:K134"/>
-    <mergeCell ref="A180:K180"/>
     <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="A190:K190"/>
     <mergeCell ref="A63:K63"/>
-    <mergeCell ref="A190:K190"/>
     <mergeCell ref="A117:E117"/>
+    <mergeCell ref="G150:K150"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20261030.xlsx
+++ b/reports/pdf_rolling5_20261030.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K196"/>
+  <dimension ref="A1:K197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-23 ~ 2026-10-30  (최근 5거래일)  ·  캡처 17/23  ·  대기: SOL, TIGER, RISE, RISE, DS, RISE</t>
+          <t>최근 5거래일 변화  ·  2026-10-23 ~ 2026-10-30  (최근 5거래일)  ·  캡처 18/23  ·  대기: TIGER, RISE, RISE, DS, RISE</t>
         </is>
       </c>
     </row>
@@ -1945,18 +1945,18 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>에이치브이엠  (신규)</t>
+          <t>티에프이  (신규)</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>4468902278</v>
+        <v>5716192914</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.11%</t>
+          <t>0.00%→2.70%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1989,18 +1989,18 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>티에프이  (신규)</t>
+          <t>에이치브이엠  (신규)</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>5716192914</v>
+        <v>4468902278</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.70%</t>
+          <t>0.00%→2.11%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -2582,23 +2582,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1544105787</v>
+        <v>-1067200544</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>1.54%→0.73%</t>
+          <t>1.26%→0.71%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>50→25</t>
+          <t>60→35</t>
         </is>
       </c>
     </row>
@@ -2626,23 +2626,23 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-1067200544</v>
+        <v>-1544105787</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.26%→0.71%</t>
+          <t>1.54%→0.73%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>60→35</t>
+          <t>50→25</t>
         </is>
       </c>
     </row>
@@ -2954,23 +2954,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>1850925633</v>
+        <v>806989840</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>1.01%→2.23%</t>
+          <t>1.12%→1.71%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>125→210</t>
+          <t>285→370</t>
         </is>
       </c>
       <c r="G68" s="17" t="n"/>
@@ -2982,23 +2982,23 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>806989840</v>
+        <v>1850925633</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>1.12%→1.71%</t>
+          <t>1.01%→2.23%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>285→370</t>
+          <t>125→210</t>
         </is>
       </c>
       <c r="G69" s="17" t="n"/>
@@ -4824,23 +4824,23 @@
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H125" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I125" s="15" t="n">
-        <v>-411106695</v>
+        <v>-231129110</v>
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>3.23%→1.56%</t>
+          <t>1.73%→0.72%</t>
         </is>
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>
@@ -4868,23 +4868,23 @@
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H126" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I126" s="15" t="n">
-        <v>-231129110</v>
+        <v>-411106695</v>
       </c>
       <c r="J126" s="16" t="inlineStr">
         <is>
-          <t>1.73%→0.72%</t>
+          <t>3.23%→1.56%</t>
         </is>
       </c>
       <c r="K126" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -4912,23 +4912,23 @@
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="H127" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I127" s="15" t="n">
-        <v>-95356545</v>
+        <v>-82558139</v>
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.64%</t>
+          <t>1.13%→0.66%</t>
         </is>
       </c>
       <c r="K127" s="13" t="inlineStr">
         <is>
-          <t>30→20</t>
+          <t>34→24</t>
         </is>
       </c>
     </row>
@@ -4956,46 +4956,46 @@
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H128" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I128" s="15" t="n">
-        <v>-82558139</v>
+        <v>-95356545</v>
       </c>
       <c r="J128" s="16" t="inlineStr">
         <is>
-          <t>1.13%→0.66%</t>
+          <t>1.07%→0.64%</t>
         </is>
       </c>
       <c r="K128" s="13" t="inlineStr">
         <is>
-          <t>34→24</t>
+          <t>30→20</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>HT로보틱스  (신규)</t>
         </is>
       </c>
       <c r="B129" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>47930873</v>
+        <v>11291225</v>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.07%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G129" s="14" t="inlineStr">
@@ -5023,23 +5023,23 @@
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (신규)</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B130" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>4174217</v>
+        <v>47930873</v>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>1.05%→1.07%</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G130" s="14" t="inlineStr">
@@ -5067,18 +5067,18 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (신규)</t>
+          <t>피엠티  (신규)</t>
         </is>
       </c>
       <c r="B131" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>11291225</v>
+        <v>4174217</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
@@ -5137,855 +5137,834 @@
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
-      <c r="A134" s="18" t="inlineStr">
-        <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B134" s="19" t="n"/>
-      <c r="C134" s="19" t="n"/>
-      <c r="D134" s="19" t="n"/>
-      <c r="E134" s="19" t="n"/>
-      <c r="F134" s="19" t="n"/>
-      <c r="G134" s="19" t="n"/>
-      <c r="H134" s="19" t="n"/>
-      <c r="I134" s="19" t="n"/>
-      <c r="J134" s="19" t="n"/>
-      <c r="K134" s="19" t="n"/>
-    </row>
-    <row r="136" ht="19" customHeight="1">
-      <c r="A136" s="3" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,113억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="n"/>
+      <c r="C134" s="4" t="n"/>
+      <c r="D134" s="4" t="n"/>
+      <c r="E134" s="4" t="n"/>
+      <c r="F134" s="4" t="n"/>
+      <c r="G134" s="4" t="n"/>
+      <c r="H134" s="4" t="n"/>
+      <c r="I134" s="4" t="n"/>
+      <c r="J134" s="4" t="n"/>
+      <c r="K134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="19" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B136" s="4" t="n"/>
-      <c r="C136" s="4" t="n"/>
-      <c r="D136" s="4" t="n"/>
-      <c r="E136" s="4" t="n"/>
-      <c r="F136" s="4" t="n"/>
-      <c r="G136" s="4" t="n"/>
-      <c r="H136" s="4" t="n"/>
-      <c r="I136" s="4" t="n"/>
-      <c r="J136" s="4" t="n"/>
-      <c r="K136" s="4" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="20" t="inlineStr">
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="n"/>
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="n"/>
+      <c r="J137" s="4" t="n"/>
+      <c r="K137" s="4" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="19" customHeight="1">
-      <c r="A139" s="18" t="inlineStr">
+    <row r="140" ht="19" customHeight="1">
+      <c r="A140" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 코리아테크액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B139" s="19" t="n"/>
-      <c r="C139" s="19" t="n"/>
-      <c r="D139" s="19" t="n"/>
-      <c r="E139" s="19" t="n"/>
-      <c r="F139" s="19" t="n"/>
-      <c r="G139" s="19" t="n"/>
-      <c r="H139" s="19" t="n"/>
-      <c r="I139" s="19" t="n"/>
-      <c r="J139" s="19" t="n"/>
-      <c r="K139" s="19" t="n"/>
-    </row>
-    <row r="141" ht="19" customHeight="1">
-      <c r="A141" s="18" t="inlineStr">
+      <c r="B140" s="20" t="n"/>
+      <c r="C140" s="20" t="n"/>
+      <c r="D140" s="20" t="n"/>
+      <c r="E140" s="20" t="n"/>
+      <c r="F140" s="20" t="n"/>
+      <c r="G140" s="20" t="n"/>
+      <c r="H140" s="20" t="n"/>
+      <c r="I140" s="20" t="n"/>
+      <c r="J140" s="20" t="n"/>
+      <c r="K140" s="20" t="n"/>
+    </row>
+    <row r="142" ht="19" customHeight="1">
+      <c r="A142" s="19" t="inlineStr">
         <is>
           <t>■ RISE 비메모리반도체액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B141" s="19" t="n"/>
-      <c r="C141" s="19" t="n"/>
-      <c r="D141" s="19" t="n"/>
-      <c r="E141" s="19" t="n"/>
-      <c r="F141" s="19" t="n"/>
-      <c r="G141" s="19" t="n"/>
-      <c r="H141" s="19" t="n"/>
-      <c r="I141" s="19" t="n"/>
-      <c r="J141" s="19" t="n"/>
-      <c r="K141" s="19" t="n"/>
-    </row>
-    <row r="143" ht="19" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
+      <c r="B142" s="20" t="n"/>
+      <c r="C142" s="20" t="n"/>
+      <c r="D142" s="20" t="n"/>
+      <c r="E142" s="20" t="n"/>
+      <c r="F142" s="20" t="n"/>
+      <c r="G142" s="20" t="n"/>
+      <c r="H142" s="20" t="n"/>
+      <c r="I142" s="20" t="n"/>
+      <c r="J142" s="20" t="n"/>
+      <c r="K142" s="20" t="n"/>
+    </row>
+    <row r="144" ht="19" customHeight="1">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 808억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B143" s="4" t="n"/>
-      <c r="C143" s="4" t="n"/>
-      <c r="D143" s="4" t="n"/>
-      <c r="E143" s="4" t="n"/>
-      <c r="F143" s="4" t="n"/>
-      <c r="G143" s="4" t="n"/>
-      <c r="H143" s="4" t="n"/>
-      <c r="I143" s="4" t="n"/>
-      <c r="J143" s="4" t="n"/>
-      <c r="K143" s="4" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="inlineStr">
+      <c r="B144" s="4" t="n"/>
+      <c r="C144" s="4" t="n"/>
+      <c r="D144" s="4" t="n"/>
+      <c r="E144" s="4" t="n"/>
+      <c r="F144" s="4" t="n"/>
+      <c r="G144" s="4" t="n"/>
+      <c r="H144" s="4" t="n"/>
+      <c r="I144" s="4" t="n"/>
+      <c r="J144" s="4" t="n"/>
+      <c r="K144" s="4" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B144" s="6" t="n"/>
-      <c r="C144" s="6" t="n"/>
-      <c r="D144" s="6" t="n"/>
-      <c r="E144" s="6" t="n"/>
-      <c r="G144" s="7" t="inlineStr">
+      <c r="B145" s="6" t="n"/>
+      <c r="C145" s="6" t="n"/>
+      <c r="D145" s="6" t="n"/>
+      <c r="E145" s="6" t="n"/>
+      <c r="G145" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H144" s="8" t="n"/>
-      <c r="I144" s="8" t="n"/>
-      <c r="J144" s="8" t="n"/>
-      <c r="K144" s="8" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="9" t="inlineStr">
+      <c r="H145" s="8" t="n"/>
+      <c r="I145" s="8" t="n"/>
+      <c r="J145" s="8" t="n"/>
+      <c r="K145" s="8" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B145" s="9" t="inlineStr">
+      <c r="B146" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="C146" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D145" s="9" t="inlineStr">
+      <c r="D146" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E145" s="9" t="inlineStr">
+      <c r="E146" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G145" s="9" t="inlineStr">
+      <c r="G146" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H145" s="9" t="inlineStr">
+      <c r="H146" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I145" s="9" t="inlineStr">
+      <c r="I146" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J145" s="9" t="inlineStr">
+      <c r="J146" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K145" s="9" t="inlineStr">
+      <c r="K146" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="10" t="inlineStr">
-        <is>
-          <t>삼성SDI</t>
-        </is>
-      </c>
-      <c r="B146" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="C146" s="11" t="n">
-        <v>767188000</v>
-      </c>
-      <c r="D146" s="12" t="inlineStr">
-        <is>
-          <t>4.41%→5.30%</t>
-        </is>
-      </c>
-      <c r="E146" s="13" t="inlineStr">
-        <is>
-          <t>209→255</t>
-        </is>
-      </c>
-      <c r="G146" s="14" t="inlineStr">
-        <is>
-          <t>대한전선</t>
-        </is>
-      </c>
-      <c r="H146" s="15" t="n">
-        <v>-1215</v>
-      </c>
-      <c r="I146" s="15" t="n">
-        <v>-772132500</v>
-      </c>
-      <c r="J146" s="16" t="inlineStr">
-        <is>
-          <t>3.04%→1.69%</t>
-        </is>
-      </c>
-      <c r="K146" s="13" t="inlineStr">
-        <is>
-          <t>3,349→2,134</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C147" s="11" t="n">
+        <v>767188000</v>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>4.41%→5.30%</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>209→255</t>
+        </is>
+      </c>
+      <c r="G147" s="14" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="H147" s="15" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="I147" s="15" t="n">
+        <v>-772132500</v>
+      </c>
+      <c r="J147" s="16" t="inlineStr">
+        <is>
+          <t>3.04%→1.69%</t>
+        </is>
+      </c>
+      <c r="K147" s="13" t="inlineStr">
+        <is>
+          <t>3,349→2,134</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="B147" s="11" t="n">
+      <c r="B148" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C147" s="11" t="n">
+      <c r="C148" s="11" t="n">
         <v>881826000</v>
       </c>
-      <c r="D147" s="12" t="inlineStr">
+      <c r="D148" s="12" t="inlineStr">
         <is>
           <t>2.98%→4.25%</t>
         </is>
       </c>
-      <c r="E147" s="13" t="inlineStr">
+      <c r="E148" s="13" t="inlineStr">
         <is>
           <t>63→85</t>
         </is>
       </c>
-      <c r="G147" s="14" t="inlineStr">
+      <c r="G148" s="14" t="inlineStr">
         <is>
           <t>삼성에스디에스</t>
         </is>
       </c>
-      <c r="H147" s="15" t="n">
+      <c r="H148" s="15" t="n">
         <v>-117</v>
       </c>
-      <c r="I147" s="15" t="n">
+      <c r="I148" s="15" t="n">
         <v>-748975500</v>
       </c>
-      <c r="J147" s="16" t="inlineStr">
+      <c r="J148" s="16" t="inlineStr">
         <is>
           <t>1.92%→0.86%</t>
         </is>
       </c>
-      <c r="K147" s="13" t="inlineStr">
+      <c r="K148" s="13" t="inlineStr">
         <is>
           <t>225→108</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="19" customHeight="1">
-      <c r="A149" s="3" t="inlineStr">
+    <row r="150" ht="19" customHeight="1">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 366억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 11종목  /  매도 15종목</t>
         </is>
       </c>
-      <c r="B149" s="4" t="n"/>
-      <c r="C149" s="4" t="n"/>
-      <c r="D149" s="4" t="n"/>
-      <c r="E149" s="4" t="n"/>
-      <c r="F149" s="4" t="n"/>
-      <c r="G149" s="4" t="n"/>
-      <c r="H149" s="4" t="n"/>
-      <c r="I149" s="4" t="n"/>
-      <c r="J149" s="4" t="n"/>
-      <c r="K149" s="4" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="5" t="inlineStr">
+      <c r="B150" s="4" t="n"/>
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
+      <c r="E150" s="4" t="n"/>
+      <c r="F150" s="4" t="n"/>
+      <c r="G150" s="4" t="n"/>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="4" t="n"/>
+      <c r="J150" s="4" t="n"/>
+      <c r="K150" s="4" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B150" s="6" t="n"/>
-      <c r="C150" s="6" t="n"/>
-      <c r="D150" s="6" t="n"/>
-      <c r="E150" s="6" t="n"/>
-      <c r="G150" s="7" t="inlineStr">
+      <c r="B151" s="6" t="n"/>
+      <c r="C151" s="6" t="n"/>
+      <c r="D151" s="6" t="n"/>
+      <c r="E151" s="6" t="n"/>
+      <c r="G151" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H150" s="8" t="n"/>
-      <c r="I150" s="8" t="n"/>
-      <c r="J150" s="8" t="n"/>
-      <c r="K150" s="8" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="9" t="inlineStr">
+      <c r="H151" s="8" t="n"/>
+      <c r="I151" s="8" t="n"/>
+      <c r="J151" s="8" t="n"/>
+      <c r="K151" s="8" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B151" s="9" t="inlineStr">
+      <c r="B152" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C151" s="9" t="inlineStr">
+      <c r="C152" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D151" s="9" t="inlineStr">
+      <c r="D152" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E151" s="9" t="inlineStr">
+      <c r="E152" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G151" s="9" t="inlineStr">
+      <c r="G152" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H151" s="9" t="inlineStr">
+      <c r="H152" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I151" s="9" t="inlineStr">
+      <c r="I152" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J151" s="9" t="inlineStr">
+      <c r="J152" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K151" s="9" t="inlineStr">
+      <c r="K152" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="10" t="inlineStr">
-        <is>
-          <t>샘씨엔에스  (신규)</t>
-        </is>
-      </c>
-      <c r="B152" s="11" t="n">
-        <v>1174</v>
-      </c>
-      <c r="C152" s="11" t="n">
-        <v>577889760</v>
-      </c>
-      <c r="D152" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.59%</t>
-        </is>
-      </c>
-      <c r="E152" s="13" t="inlineStr">
-        <is>
-          <t>0→1,174</t>
-        </is>
-      </c>
-      <c r="G152" s="14" t="inlineStr">
-        <is>
-          <t>솔루엠  (편출)</t>
-        </is>
-      </c>
-      <c r="H152" s="15" t="n">
-        <v>-574</v>
-      </c>
-      <c r="I152" s="15" t="n">
-        <v>-243972960</v>
-      </c>
-      <c r="J152" s="16" t="inlineStr">
-        <is>
-          <t>0.71%→0.00%</t>
-        </is>
-      </c>
-      <c r="K152" s="13" t="inlineStr">
-        <is>
-          <t>574→0</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>한화비전  (신규)</t>
+          <t>샘씨엔에스  (신규)</t>
         </is>
       </c>
       <c r="B153" s="11" t="n">
-        <v>997</v>
+        <v>1174</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>1370675600</v>
+        <v>577889760</v>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.78%</t>
+          <t>0.00%→1.59%</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>0→997</t>
+          <t>0→1,174</t>
         </is>
       </c>
       <c r="G153" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>솔루엠  (편출)</t>
         </is>
       </c>
       <c r="H153" s="15" t="n">
-        <v>-541</v>
+        <v>-574</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>-691506200</v>
+        <v>-243972960</v>
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>3.39%→1.13%</t>
+          <t>0.71%→0.00%</t>
         </is>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
-          <t>861→320</t>
+          <t>574→0</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스  (신규)</t>
+          <t>한화비전  (신규)</t>
         </is>
       </c>
       <c r="B154" s="11" t="n">
-        <v>324</v>
+        <v>997</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>562464000</v>
+        <v>1370675600</v>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.55%</t>
+          <t>0.00%→3.78%</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>0→324</t>
+          <t>0→997</t>
         </is>
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>두산퓨얼셀  (편출)</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H154" s="15" t="n">
-        <v>-513</v>
+        <v>-541</v>
       </c>
       <c r="I154" s="15" t="n">
-        <v>-480475800</v>
+        <v>-691506200</v>
       </c>
       <c r="J154" s="16" t="inlineStr">
         <is>
-          <t>1.40%→0.00%</t>
+          <t>3.39%→1.13%</t>
         </is>
       </c>
       <c r="K154" s="13" t="inlineStr">
         <is>
-          <t>513→0</t>
+          <t>861→320</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>ISC  (신규)</t>
+          <t>인텍플러스  (신규)</t>
         </is>
       </c>
       <c r="B155" s="11" t="n">
-        <v>165</v>
+        <v>324</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>767844000</v>
+        <v>562464000</v>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.12%</t>
+          <t>0.00%→1.55%</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>0→165</t>
+          <t>0→324</t>
         </is>
       </c>
       <c r="G155" s="14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>두산퓨얼셀  (편출)</t>
         </is>
       </c>
       <c r="H155" s="15" t="n">
-        <v>-473</v>
+        <v>-513</v>
       </c>
       <c r="I155" s="15" t="n">
-        <v>-750934800</v>
+        <v>-480475800</v>
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>2.95%→0.50%</t>
+          <t>1.40%→0.00%</t>
         </is>
       </c>
       <c r="K155" s="13" t="inlineStr">
         <is>
-          <t>588→115</t>
+          <t>513→0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔  (신규)</t>
+          <t>ISC  (신규)</t>
         </is>
       </c>
       <c r="B156" s="11" t="n">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>73038000</v>
+        <v>767844000</v>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.20%</t>
+          <t>0.00%→2.12%</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>0→111</t>
+          <t>0→165</t>
         </is>
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>현대건설  (편출)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="H156" s="15" t="n">
-        <v>-216</v>
+        <v>-473</v>
       </c>
       <c r="I156" s="15" t="n">
-        <v>-562464000</v>
+        <v>-750934800</v>
       </c>
       <c r="J156" s="16" t="inlineStr">
         <is>
-          <t>1.64%→0.00%</t>
+          <t>2.95%→0.50%</t>
         </is>
       </c>
       <c r="K156" s="13" t="inlineStr">
         <is>
-          <t>216→0</t>
+          <t>588→115</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>에코프로에이치엔  (신규)</t>
         </is>
       </c>
       <c r="B157" s="11" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>163800000</v>
+        <v>73038000</v>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>4.80%→5.29%</t>
+          <t>0.00%→0.20%</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>644→704</t>
+          <t>0→111</t>
         </is>
       </c>
       <c r="G157" s="14" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>현대건설  (편출)</t>
         </is>
       </c>
       <c r="H157" s="15" t="n">
-        <v>-191</v>
+        <v>-216</v>
       </c>
       <c r="I157" s="15" t="n">
-        <v>-277026400</v>
+        <v>-562464000</v>
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>1.54%→0.84%</t>
+          <t>1.64%→0.00%</t>
         </is>
       </c>
       <c r="K157" s="13" t="inlineStr">
         <is>
-          <t>401→210</t>
+          <t>216→0</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B158" s="11" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>1367296000</v>
+        <v>163800000</v>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>5.88%→10.71%</t>
+          <t>4.80%→5.29%</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>59→91</t>
+          <t>644→704</t>
         </is>
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>비에이치아이  (편출)</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="H158" s="15" t="n">
-        <v>-157</v>
+        <v>-191</v>
       </c>
       <c r="I158" s="15" t="n">
-        <v>-201776400</v>
+        <v>-277026400</v>
       </c>
       <c r="J158" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.00%</t>
+          <t>1.54%→0.84%</t>
         </is>
       </c>
       <c r="K158" s="13" t="inlineStr">
         <is>
-          <t>157→0</t>
+          <t>401→210</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B159" s="11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>168565600</v>
+        <v>1367296000</v>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>5.37%→6.32%</t>
+          <t>5.88%→10.71%</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>391→422</t>
+          <t>59→91</t>
         </is>
       </c>
       <c r="G159" s="14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>비에이치아이  (편출)</t>
         </is>
       </c>
       <c r="H159" s="15" t="n">
-        <v>-138</v>
+        <v>-157</v>
       </c>
       <c r="I159" s="15" t="n">
-        <v>-896448000</v>
+        <v>-201776400</v>
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>8.52%→6.26%</t>
+          <t>0.59%→0.00%</t>
         </is>
       </c>
       <c r="K159" s="13" t="inlineStr">
         <is>
-          <t>488→350</t>
+          <t>157→0</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B160" s="11" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>118431600</v>
+        <v>168565600</v>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>5.23%→5.77%</t>
+          <t>5.37%→6.32%</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>384→407</t>
+          <t>391→422</t>
         </is>
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>SK텔레콤  (편출)</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="H160" s="15" t="n">
-        <v>-77</v>
+        <v>-138</v>
       </c>
       <c r="I160" s="15" t="n">
-        <v>-164287200</v>
+        <v>-896448000</v>
       </c>
       <c r="J160" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.00%</t>
+          <t>8.52%→6.26%</t>
         </is>
       </c>
       <c r="K160" s="13" t="inlineStr">
         <is>
-          <t>77→0</t>
+          <t>488→350</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B161" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>331408000</v>
+        <v>118431600</v>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>5.59%→6.47%</t>
+          <t>5.23%→5.77%</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>134→156</t>
+          <t>384→407</t>
         </is>
       </c>
       <c r="G161" s="14" t="inlineStr">
         <is>
-          <t>DB하이텍  (편출)</t>
+          <t>SK텔레콤  (편출)</t>
         </is>
       </c>
       <c r="H161" s="15" t="n">
-        <v>-69</v>
+        <v>-77</v>
       </c>
       <c r="I161" s="15" t="n">
-        <v>-191074800</v>
+        <v>-164287200</v>
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.00%</t>
+          <t>0.48%→0.00%</t>
         </is>
       </c>
       <c r="K161" s="13" t="inlineStr">
         <is>
-          <t>69→0</t>
+          <t>77→0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
         <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C162" s="11" t="n">
+        <v>331408000</v>
+      </c>
+      <c r="D162" s="12" t="inlineStr">
+        <is>
+          <t>5.59%→6.47%</t>
+        </is>
+      </c>
+      <c r="E162" s="13" t="inlineStr">
+        <is>
+          <t>134→156</t>
+        </is>
+      </c>
+      <c r="G162" s="14" t="inlineStr">
+        <is>
+          <t>DB하이텍  (편출)</t>
+        </is>
+      </c>
+      <c r="H162" s="15" t="n">
+        <v>-69</v>
+      </c>
+      <c r="I162" s="15" t="n">
+        <v>-191074800</v>
+      </c>
+      <c r="J162" s="16" t="inlineStr">
+        <is>
+          <t>0.56%→0.00%</t>
+        </is>
+      </c>
+      <c r="K162" s="13" t="inlineStr">
+        <is>
+          <t>69→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="10" t="inlineStr">
+        <is>
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="B162" s="11" t="n">
+      <c r="B163" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C162" s="11" t="n">
+      <c r="C163" s="11" t="n">
         <v>108612000</v>
       </c>
-      <c r="D162" s="12" t="inlineStr">
+      <c r="D163" s="12" t="inlineStr">
         <is>
           <t>1.12%→1.50%</t>
         </is>
       </c>
-      <c r="E162" s="13" t="inlineStr">
+      <c r="E163" s="13" t="inlineStr">
         <is>
           <t>12→15</t>
         </is>
       </c>
-      <c r="G162" s="14" t="inlineStr">
+      <c r="G163" s="14" t="inlineStr">
         <is>
           <t>피에스케이</t>
         </is>
       </c>
-      <c r="H162" s="15" t="n">
+      <c r="H163" s="15" t="n">
         <v>-43</v>
       </c>
-      <c r="I162" s="15" t="n">
+      <c r="I163" s="15" t="n">
         <v>-144841200</v>
       </c>
-      <c r="J162" s="16" t="inlineStr">
+      <c r="J163" s="16" t="inlineStr">
         <is>
           <t>3.04%→2.55%</t>
         </is>
       </c>
-      <c r="K162" s="13" t="inlineStr">
+      <c r="K163" s="13" t="inlineStr">
         <is>
           <t>318→275</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="17" t="n"/>
-      <c r="B163" s="17" t="n"/>
-      <c r="C163" s="17" t="n"/>
-      <c r="D163" s="17" t="n"/>
-      <c r="E163" s="17" t="n"/>
-      <c r="G163" s="14" t="inlineStr">
-        <is>
-          <t>LG에너지솔루션</t>
-        </is>
-      </c>
-      <c r="H163" s="15" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I163" s="15" t="n">
-        <v>-299040000</v>
-      </c>
-      <c r="J163" s="16" t="inlineStr">
-        <is>
-          <t>4.19%→2.80%</t>
-        </is>
-      </c>
-      <c r="K163" s="13" t="inlineStr">
-        <is>
-          <t>132→102</t>
         </is>
       </c>
     </row>
@@ -5997,23 +5976,23 @@
       <c r="E164" s="17" t="n"/>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="H164" s="15" t="n">
-        <v>-24</v>
+        <v>-30</v>
       </c>
       <c r="I164" s="15" t="n">
-        <v>-18480000</v>
+        <v>-299040000</v>
       </c>
       <c r="J164" s="16" t="inlineStr">
         <is>
-          <t>3.01%→2.77%</t>
+          <t>4.19%→2.80%</t>
         </is>
       </c>
       <c r="K164" s="13" t="inlineStr">
         <is>
-          <t>1,328→1,304</t>
+          <t>132→102</t>
         </is>
       </c>
     </row>
@@ -6025,23 +6004,23 @@
       <c r="E165" s="17" t="n"/>
       <c r="G165" s="14" t="inlineStr">
         <is>
-          <t>두산  (편출)</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="H165" s="15" t="n">
-        <v>-19</v>
+        <v>-24</v>
       </c>
       <c r="I165" s="15" t="n">
-        <v>-536788000</v>
+        <v>-18480000</v>
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>1.56%→0.00%</t>
+          <t>3.01%→2.77%</t>
         </is>
       </c>
       <c r="K165" s="13" t="inlineStr">
         <is>
-          <t>19→0</t>
+          <t>1,328→1,304</t>
         </is>
       </c>
     </row>
@@ -6053,207 +6032,207 @@
       <c r="E166" s="17" t="n"/>
       <c r="G166" s="14" t="inlineStr">
         <is>
+          <t>두산  (편출)</t>
+        </is>
+      </c>
+      <c r="H166" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I166" s="15" t="n">
+        <v>-536788000</v>
+      </c>
+      <c r="J166" s="16" t="inlineStr">
+        <is>
+          <t>1.56%→0.00%</t>
+        </is>
+      </c>
+      <c r="K166" s="13" t="inlineStr">
+        <is>
+          <t>19→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="17" t="n"/>
+      <c r="B167" s="17" t="n"/>
+      <c r="C167" s="17" t="n"/>
+      <c r="D167" s="17" t="n"/>
+      <c r="E167" s="17" t="n"/>
+      <c r="G167" s="14" t="inlineStr">
+        <is>
           <t>HD현대일렉트릭  (편출)</t>
         </is>
       </c>
-      <c r="H166" s="15" t="n">
+      <c r="H167" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I166" s="15" t="n">
+      <c r="I167" s="15" t="n">
         <v>-178360000</v>
       </c>
-      <c r="J166" s="16" t="inlineStr">
+      <c r="J167" s="16" t="inlineStr">
         <is>
           <t>0.52%→0.00%</t>
         </is>
       </c>
-      <c r="K166" s="13" t="inlineStr">
+      <c r="K167" s="13" t="inlineStr">
         <is>
           <t>13→0</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="19" customHeight="1">
-      <c r="A168" s="3" t="inlineStr">
+    <row r="169" ht="19" customHeight="1">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 540억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
-      <c r="B168" s="4" t="n"/>
-      <c r="C168" s="4" t="n"/>
-      <c r="D168" s="4" t="n"/>
-      <c r="E168" s="4" t="n"/>
-      <c r="F168" s="4" t="n"/>
-      <c r="G168" s="4" t="n"/>
-      <c r="H168" s="4" t="n"/>
-      <c r="I168" s="4" t="n"/>
-      <c r="J168" s="4" t="n"/>
-      <c r="K168" s="4" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="inlineStr">
+      <c r="B169" s="4" t="n"/>
+      <c r="C169" s="4" t="n"/>
+      <c r="D169" s="4" t="n"/>
+      <c r="E169" s="4" t="n"/>
+      <c r="F169" s="4" t="n"/>
+      <c r="G169" s="4" t="n"/>
+      <c r="H169" s="4" t="n"/>
+      <c r="I169" s="4" t="n"/>
+      <c r="J169" s="4" t="n"/>
+      <c r="K169" s="4" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B169" s="6" t="n"/>
-      <c r="C169" s="6" t="n"/>
-      <c r="D169" s="6" t="n"/>
-      <c r="E169" s="6" t="n"/>
-      <c r="G169" s="7" t="inlineStr">
+      <c r="B170" s="6" t="n"/>
+      <c r="C170" s="6" t="n"/>
+      <c r="D170" s="6" t="n"/>
+      <c r="E170" s="6" t="n"/>
+      <c r="G170" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H169" s="8" t="n"/>
-      <c r="I169" s="8" t="n"/>
-      <c r="J169" s="8" t="n"/>
-      <c r="K169" s="8" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="9" t="inlineStr">
+      <c r="H170" s="8" t="n"/>
+      <c r="I170" s="8" t="n"/>
+      <c r="J170" s="8" t="n"/>
+      <c r="K170" s="8" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B170" s="9" t="inlineStr">
+      <c r="B171" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C170" s="9" t="inlineStr">
+      <c r="C171" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D170" s="9" t="inlineStr">
+      <c r="D171" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E170" s="9" t="inlineStr">
+      <c r="E171" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G170" s="9" t="inlineStr">
+      <c r="G171" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H170" s="9" t="inlineStr">
+      <c r="H171" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I170" s="9" t="inlineStr">
+      <c r="I171" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J170" s="9" t="inlineStr">
+      <c r="J171" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K170" s="9" t="inlineStr">
+      <c r="K171" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="10" t="inlineStr">
-        <is>
-          <t>디케이티  (신규)</t>
-        </is>
-      </c>
-      <c r="B171" s="11" t="n">
-        <v>298</v>
-      </c>
-      <c r="C171" s="11" t="n">
-        <v>727120000</v>
-      </c>
-      <c r="D171" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.34%</t>
-        </is>
-      </c>
-      <c r="E171" s="13" t="inlineStr">
-        <is>
-          <t>0→298</t>
-        </is>
-      </c>
-      <c r="G171" s="14" t="inlineStr">
-        <is>
-          <t>기가비스  (편출)</t>
-        </is>
-      </c>
-      <c r="H171" s="15" t="n">
-        <v>-275</v>
-      </c>
-      <c r="I171" s="15" t="n">
-        <v>-2871000000</v>
-      </c>
-      <c r="J171" s="16" t="inlineStr">
-        <is>
-          <t>5.23%→0.00%</t>
-        </is>
-      </c>
-      <c r="K171" s="13" t="inlineStr">
-        <is>
-          <t>275→0</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
         <is>
-          <t>GST  (신규)</t>
+          <t>디케이티  (신규)</t>
         </is>
       </c>
       <c r="B172" s="11" t="n">
-        <v>154</v>
+        <v>298</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>681450000</v>
+        <v>727120000</v>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.25%</t>
+          <t>0.00%→1.34%</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>0→154</t>
-        </is>
-      </c>
-      <c r="G172" s="17" t="n"/>
-      <c r="H172" s="17" t="n"/>
-      <c r="I172" s="17" t="n"/>
-      <c r="J172" s="17" t="n"/>
-      <c r="K172" s="17" t="n"/>
+          <t>0→298</t>
+        </is>
+      </c>
+      <c r="G172" s="14" t="inlineStr">
+        <is>
+          <t>기가비스  (편출)</t>
+        </is>
+      </c>
+      <c r="H172" s="15" t="n">
+        <v>-275</v>
+      </c>
+      <c r="I172" s="15" t="n">
+        <v>-2871000000</v>
+      </c>
+      <c r="J172" s="16" t="inlineStr">
+        <is>
+          <t>5.23%→0.00%</t>
+        </is>
+      </c>
+      <c r="K172" s="13" t="inlineStr">
+        <is>
+          <t>275→0</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>GST  (신규)</t>
         </is>
       </c>
       <c r="B173" s="11" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>453330000</v>
+        <v>681450000</v>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>0.95%→1.79%</t>
+          <t>0.00%→1.25%</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>168→314</t>
+          <t>0→154</t>
         </is>
       </c>
       <c r="G173" s="17" t="n"/>
@@ -6265,23 +6244,23 @@
     <row r="174">
       <c r="A174" s="10" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B174" s="11" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>451935000</v>
+        <v>453330000</v>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.84%</t>
+          <t>0.95%→1.79%</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>147→268</t>
+          <t>168→314</t>
         </is>
       </c>
       <c r="G174" s="17" t="n"/>
@@ -6293,23 +6272,23 @@
     <row r="175">
       <c r="A175" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="B175" s="11" t="n">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>602020000</v>
+        <v>451935000</v>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>6.12%→7.28%</t>
+          <t>1.00%→1.84%</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>173→204</t>
+          <t>147→268</t>
         </is>
       </c>
       <c r="G175" s="17" t="n"/>
@@ -6318,363 +6297,392 @@
       <c r="J175" s="17" t="n"/>
       <c r="K175" s="17" t="n"/>
     </row>
-    <row r="177" ht="19" customHeight="1">
-      <c r="A177" s="18" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C176" s="11" t="n">
+        <v>602020000</v>
+      </c>
+      <c r="D176" s="12" t="inlineStr">
+        <is>
+          <t>6.12%→7.28%</t>
+        </is>
+      </c>
+      <c r="E176" s="13" t="inlineStr">
+        <is>
+          <t>173→204</t>
+        </is>
+      </c>
+      <c r="G176" s="17" t="n"/>
+      <c r="H176" s="17" t="n"/>
+      <c r="I176" s="17" t="n"/>
+      <c r="J176" s="17" t="n"/>
+      <c r="K176" s="17" t="n"/>
+    </row>
+    <row r="178" ht="19" customHeight="1">
+      <c r="A178" s="19" t="inlineStr">
         <is>
           <t>■ RISE 반도체소부장액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B177" s="19" t="n"/>
-      <c r="C177" s="19" t="n"/>
-      <c r="D177" s="19" t="n"/>
-      <c r="E177" s="19" t="n"/>
-      <c r="F177" s="19" t="n"/>
-      <c r="G177" s="19" t="n"/>
-      <c r="H177" s="19" t="n"/>
-      <c r="I177" s="19" t="n"/>
-      <c r="J177" s="19" t="n"/>
-      <c r="K177" s="19" t="n"/>
-    </row>
-    <row r="179" ht="19" customHeight="1">
-      <c r="A179" s="18" t="inlineStr">
+      <c r="B178" s="20" t="n"/>
+      <c r="C178" s="20" t="n"/>
+      <c r="D178" s="20" t="n"/>
+      <c r="E178" s="20" t="n"/>
+      <c r="F178" s="20" t="n"/>
+      <c r="G178" s="20" t="n"/>
+      <c r="H178" s="20" t="n"/>
+      <c r="I178" s="20" t="n"/>
+      <c r="J178" s="20" t="n"/>
+      <c r="K178" s="20" t="n"/>
+    </row>
+    <row r="180" ht="19" customHeight="1">
+      <c r="A180" s="19" t="inlineStr">
         <is>
           <t>■ DS AI반도체액티브  (DS)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B179" s="19" t="n"/>
-      <c r="C179" s="19" t="n"/>
-      <c r="D179" s="19" t="n"/>
-      <c r="E179" s="19" t="n"/>
-      <c r="F179" s="19" t="n"/>
-      <c r="G179" s="19" t="n"/>
-      <c r="H179" s="19" t="n"/>
-      <c r="I179" s="19" t="n"/>
-      <c r="J179" s="19" t="n"/>
-      <c r="K179" s="19" t="n"/>
-    </row>
-    <row r="181" ht="19" customHeight="1">
-      <c r="A181" s="18" t="inlineStr">
+      <c r="B180" s="20" t="n"/>
+      <c r="C180" s="20" t="n"/>
+      <c r="D180" s="20" t="n"/>
+      <c r="E180" s="20" t="n"/>
+      <c r="F180" s="20" t="n"/>
+      <c r="G180" s="20" t="n"/>
+      <c r="H180" s="20" t="n"/>
+      <c r="I180" s="20" t="n"/>
+      <c r="J180" s="20" t="n"/>
+      <c r="K180" s="20" t="n"/>
+    </row>
+    <row r="182" ht="19" customHeight="1">
+      <c r="A182" s="19" t="inlineStr">
         <is>
           <t>■ RISE 2차전지액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B181" s="19" t="n"/>
-      <c r="C181" s="19" t="n"/>
-      <c r="D181" s="19" t="n"/>
-      <c r="E181" s="19" t="n"/>
-      <c r="F181" s="19" t="n"/>
-      <c r="G181" s="19" t="n"/>
-      <c r="H181" s="19" t="n"/>
-      <c r="I181" s="19" t="n"/>
-      <c r="J181" s="19" t="n"/>
-      <c r="K181" s="19" t="n"/>
-    </row>
-    <row r="183" ht="19" customHeight="1">
-      <c r="A183" s="3" t="inlineStr">
+      <c r="B182" s="20" t="n"/>
+      <c r="C182" s="20" t="n"/>
+      <c r="D182" s="20" t="n"/>
+      <c r="E182" s="20" t="n"/>
+      <c r="F182" s="20" t="n"/>
+      <c r="G182" s="20" t="n"/>
+      <c r="H182" s="20" t="n"/>
+      <c r="I182" s="20" t="n"/>
+      <c r="J182" s="20" t="n"/>
+      <c r="K182" s="20" t="n"/>
+    </row>
+    <row r="184" ht="19" customHeight="1">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 281억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B183" s="4" t="n"/>
-      <c r="C183" s="4" t="n"/>
-      <c r="D183" s="4" t="n"/>
-      <c r="E183" s="4" t="n"/>
-      <c r="F183" s="4" t="n"/>
-      <c r="G183" s="4" t="n"/>
-      <c r="H183" s="4" t="n"/>
-      <c r="I183" s="4" t="n"/>
-      <c r="J183" s="4" t="n"/>
-      <c r="K183" s="4" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="5" t="inlineStr">
+      <c r="B184" s="4" t="n"/>
+      <c r="C184" s="4" t="n"/>
+      <c r="D184" s="4" t="n"/>
+      <c r="E184" s="4" t="n"/>
+      <c r="F184" s="4" t="n"/>
+      <c r="G184" s="4" t="n"/>
+      <c r="H184" s="4" t="n"/>
+      <c r="I184" s="4" t="n"/>
+      <c r="J184" s="4" t="n"/>
+      <c r="K184" s="4" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B184" s="6" t="n"/>
-      <c r="C184" s="6" t="n"/>
-      <c r="D184" s="6" t="n"/>
-      <c r="E184" s="6" t="n"/>
-      <c r="G184" s="7" t="inlineStr">
+      <c r="B185" s="6" t="n"/>
+      <c r="C185" s="6" t="n"/>
+      <c r="D185" s="6" t="n"/>
+      <c r="E185" s="6" t="n"/>
+      <c r="G185" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H184" s="8" t="n"/>
-      <c r="I184" s="8" t="n"/>
-      <c r="J184" s="8" t="n"/>
-      <c r="K184" s="8" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="9" t="inlineStr">
+      <c r="H185" s="8" t="n"/>
+      <c r="I185" s="8" t="n"/>
+      <c r="J185" s="8" t="n"/>
+      <c r="K185" s="8" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B185" s="9" t="inlineStr">
+      <c r="B186" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C185" s="9" t="inlineStr">
+      <c r="C186" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D185" s="9" t="inlineStr">
+      <c r="D186" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E185" s="9" t="inlineStr">
+      <c r="E186" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G185" s="9" t="inlineStr">
+      <c r="G186" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H185" s="9" t="inlineStr">
+      <c r="H186" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I185" s="9" t="inlineStr">
+      <c r="I186" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J185" s="9" t="inlineStr">
+      <c r="J186" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K185" s="9" t="inlineStr">
+      <c r="K186" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="10" t="inlineStr">
-        <is>
-          <t>에코프로에이치엔</t>
-        </is>
-      </c>
-      <c r="B186" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="C186" s="11" t="n">
-        <v>55271980</v>
-      </c>
-      <c r="D186" s="12" t="inlineStr">
-        <is>
-          <t>0.51%→0.73%</t>
-        </is>
-      </c>
-      <c r="E186" s="13" t="inlineStr">
-        <is>
-          <t>112→154</t>
-        </is>
-      </c>
-      <c r="G186" s="14" t="inlineStr">
-        <is>
-          <t>상신이디피</t>
-        </is>
-      </c>
-      <c r="H186" s="15" t="n">
-        <v>-95</v>
-      </c>
-      <c r="I186" s="15" t="n">
-        <v>-136989951</v>
-      </c>
-      <c r="J186" s="16" t="inlineStr">
-        <is>
-          <t>8.88%→9.20%</t>
-        </is>
-      </c>
-      <c r="K186" s="13" t="inlineStr">
-        <is>
-          <t>1,876→1,781</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="10" t="inlineStr">
         <is>
+          <t>에코프로에이치엔</t>
+        </is>
+      </c>
+      <c r="B187" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C187" s="11" t="n">
+        <v>55271980</v>
+      </c>
+      <c r="D187" s="12" t="inlineStr">
+        <is>
+          <t>0.51%→0.73%</t>
+        </is>
+      </c>
+      <c r="E187" s="13" t="inlineStr">
+        <is>
+          <t>112→154</t>
+        </is>
+      </c>
+      <c r="G187" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H187" s="15" t="n">
+        <v>-95</v>
+      </c>
+      <c r="I187" s="15" t="n">
+        <v>-136989951</v>
+      </c>
+      <c r="J187" s="16" t="inlineStr">
+        <is>
+          <t>8.88%→9.20%</t>
+        </is>
+      </c>
+      <c r="K187" s="13" t="inlineStr">
+        <is>
+          <t>1,876→1,781</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="10" t="inlineStr">
+        <is>
           <t>한중엔시에스</t>
         </is>
       </c>
-      <c r="B187" s="11" t="n">
+      <c r="B188" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="C187" s="11" t="n">
+      <c r="C188" s="11" t="n">
         <v>85388770</v>
       </c>
-      <c r="D187" s="12" t="inlineStr">
+      <c r="D188" s="12" t="inlineStr">
         <is>
           <t>6.94%→7.49%</t>
         </is>
       </c>
-      <c r="E187" s="13" t="inlineStr">
+      <c r="E188" s="13" t="inlineStr">
         <is>
           <t>752→784</t>
         </is>
       </c>
-      <c r="G187" s="14" t="inlineStr">
+      <c r="G188" s="14" t="inlineStr">
         <is>
           <t>HD현대일렉트릭</t>
         </is>
       </c>
-      <c r="H187" s="15" t="n">
+      <c r="H188" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I187" s="15" t="n">
+      <c r="I188" s="15" t="n">
         <v>-74003974</v>
       </c>
-      <c r="J187" s="16" t="inlineStr">
+      <c r="J188" s="16" t="inlineStr">
         <is>
           <t>2.20%→1.85%</t>
         </is>
       </c>
-      <c r="K187" s="13" t="inlineStr">
+      <c r="K188" s="13" t="inlineStr">
         <is>
           <t>24→21</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="19" customHeight="1">
-      <c r="A189" s="3" t="inlineStr">
+    <row r="190" ht="19" customHeight="1">
+      <c r="A190" s="3" t="inlineStr">
         <is>
           <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 157억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B189" s="4" t="n"/>
-      <c r="C189" s="4" t="n"/>
-      <c r="D189" s="4" t="n"/>
-      <c r="E189" s="4" t="n"/>
-      <c r="F189" s="4" t="n"/>
-      <c r="G189" s="4" t="n"/>
-      <c r="H189" s="4" t="n"/>
-      <c r="I189" s="4" t="n"/>
-      <c r="J189" s="4" t="n"/>
-      <c r="K189" s="4" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="20" t="inlineStr">
+      <c r="B190" s="4" t="n"/>
+      <c r="C190" s="4" t="n"/>
+      <c r="D190" s="4" t="n"/>
+      <c r="E190" s="4" t="n"/>
+      <c r="F190" s="4" t="n"/>
+      <c r="G190" s="4" t="n"/>
+      <c r="H190" s="4" t="n"/>
+      <c r="I190" s="4" t="n"/>
+      <c r="J190" s="4" t="n"/>
+      <c r="K190" s="4" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="19" customHeight="1">
-      <c r="A192" s="3" t="inlineStr">
+    <row r="193" ht="19" customHeight="1">
+      <c r="A193" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 87억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B192" s="4" t="n"/>
-      <c r="C192" s="4" t="n"/>
-      <c r="D192" s="4" t="n"/>
-      <c r="E192" s="4" t="n"/>
-      <c r="F192" s="4" t="n"/>
-      <c r="G192" s="4" t="n"/>
-      <c r="H192" s="4" t="n"/>
-      <c r="I192" s="4" t="n"/>
-      <c r="J192" s="4" t="n"/>
-      <c r="K192" s="4" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="20" t="inlineStr">
+      <c r="B193" s="4" t="n"/>
+      <c r="C193" s="4" t="n"/>
+      <c r="D193" s="4" t="n"/>
+      <c r="E193" s="4" t="n"/>
+      <c r="F193" s="4" t="n"/>
+      <c r="G193" s="4" t="n"/>
+      <c r="H193" s="4" t="n"/>
+      <c r="I193" s="4" t="n"/>
+      <c r="J193" s="4" t="n"/>
+      <c r="K193" s="4" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="19" customHeight="1">
-      <c r="A195" s="3" t="inlineStr">
+    <row r="196" ht="19" customHeight="1">
+      <c r="A196" s="3" t="inlineStr">
         <is>
           <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 58억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B195" s="4" t="n"/>
-      <c r="C195" s="4" t="n"/>
-      <c r="D195" s="4" t="n"/>
-      <c r="E195" s="4" t="n"/>
-      <c r="F195" s="4" t="n"/>
-      <c r="G195" s="4" t="n"/>
-      <c r="H195" s="4" t="n"/>
-      <c r="I195" s="4" t="n"/>
-      <c r="J195" s="4" t="n"/>
-      <c r="K195" s="4" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="20" t="inlineStr">
+      <c r="B196" s="4" t="n"/>
+      <c r="C196" s="4" t="n"/>
+      <c r="D196" s="4" t="n"/>
+      <c r="E196" s="4" t="n"/>
+      <c r="F196" s="4" t="n"/>
+      <c r="G196" s="4" t="n"/>
+      <c r="H196" s="4" t="n"/>
+      <c r="I196" s="4" t="n"/>
+      <c r="J196" s="4" t="n"/>
+      <c r="K196" s="4" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="A143:K143"/>
+  <mergeCells count="56">
+    <mergeCell ref="G185:K185"/>
     <mergeCell ref="A73:E73"/>
     <mergeCell ref="A64:E64"/>
     <mergeCell ref="A82:E82"/>
     <mergeCell ref="G117:K117"/>
-    <mergeCell ref="A169:E169"/>
-    <mergeCell ref="G169:K169"/>
+    <mergeCell ref="A142:K142"/>
+    <mergeCell ref="A182:K182"/>
+    <mergeCell ref="G151:K151"/>
+    <mergeCell ref="A178:K178"/>
+    <mergeCell ref="A191:K191"/>
     <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A138:K138"/>
+    <mergeCell ref="G145:K145"/>
+    <mergeCell ref="A169:K169"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A94:K94"/>
-    <mergeCell ref="A168:K168"/>
+    <mergeCell ref="G170:K170"/>
+    <mergeCell ref="A197:K197"/>
     <mergeCell ref="G82:K82"/>
     <mergeCell ref="G101:K101"/>
     <mergeCell ref="A196:K196"/>
     <mergeCell ref="A137:K137"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="G37:K37"/>
-    <mergeCell ref="A177:K177"/>
-    <mergeCell ref="A183:K183"/>
-    <mergeCell ref="G184:K184"/>
     <mergeCell ref="A193:K193"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="G18:K18"/>
-    <mergeCell ref="A189:K189"/>
-    <mergeCell ref="A136:K136"/>
-    <mergeCell ref="A192:K192"/>
-    <mergeCell ref="A149:K149"/>
+    <mergeCell ref="A145:E145"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A139:K139"/>
-    <mergeCell ref="A179:K179"/>
-    <mergeCell ref="A195:K195"/>
     <mergeCell ref="G95:K95"/>
+    <mergeCell ref="A151:E151"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A185:E185"/>
+    <mergeCell ref="A194:K194"/>
     <mergeCell ref="A116:K116"/>
-    <mergeCell ref="A150:E150"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G73:K73"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A141:K141"/>
+    <mergeCell ref="A144:K144"/>
     <mergeCell ref="G64:K64"/>
-    <mergeCell ref="A144:E144"/>
-    <mergeCell ref="A181:K181"/>
-    <mergeCell ref="A184:E184"/>
+    <mergeCell ref="A150:K150"/>
+    <mergeCell ref="A135:K135"/>
+    <mergeCell ref="A184:K184"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A100:K100"/>
-    <mergeCell ref="G144:K144"/>
+    <mergeCell ref="A140:K140"/>
     <mergeCell ref="A72:K72"/>
     <mergeCell ref="A134:K134"/>
+    <mergeCell ref="A180:K180"/>
     <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="A63:K63"/>
     <mergeCell ref="A190:K190"/>
-    <mergeCell ref="A63:K63"/>
     <mergeCell ref="A117:E117"/>
-    <mergeCell ref="G150:K150"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20261030.xlsx
+++ b/reports/pdf_rolling5_20261030.xlsx
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-884660036</v>
+        <v>-846888034</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.69%</t>
+          <t>1.19%→0.94%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>18→14</t>
+          <t>24→20</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1048,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-846888034</v>
+        <v>-884660036</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.94%</t>
+          <t>1.05%→0.69%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>24→20</t>
+          <t>18→14</t>
         </is>
       </c>
     </row>
@@ -1945,18 +1945,18 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>티에프이  (신규)</t>
+          <t>한양디지텍  (신규)</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>5716192914</v>
+        <v>2634651343</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.70%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1989,18 +1989,18 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>에이치브이엠  (신규)</t>
+          <t>티에프이  (신규)</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>4468902278</v>
+        <v>5716192914</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.11%</t>
+          <t>0.00%→2.70%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -2033,18 +2033,18 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍  (신규)</t>
+          <t>에이치브이엠  (신규)</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>2634651343</v>
+        <v>4468902278</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>0.00%→2.11%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -2726,23 +2726,23 @@
       <c r="E60" s="17" t="n"/>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H60" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-578522745</v>
+        <v>-5259297681</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>1.46%→1.16%</t>
+          <t>3.72%→1.44%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>100→81</t>
+          <t>30→11</t>
         </is>
       </c>
     </row>
@@ -2754,23 +2754,23 @@
       <c r="E61" s="17" t="n"/>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-5259297681</v>
+        <v>-578522745</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>3.72%→1.44%</t>
+          <t>1.46%→1.16%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
-          <t>30→11</t>
+          <t>100→81</t>
         </is>
       </c>
     </row>
@@ -4824,23 +4824,23 @@
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H125" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I125" s="15" t="n">
-        <v>-231129110</v>
+        <v>-411106695</v>
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>1.73%→0.72%</t>
+          <t>3.23%→1.56%</t>
         </is>
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -4868,23 +4868,23 @@
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H126" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I126" s="15" t="n">
-        <v>-411106695</v>
+        <v>-231129110</v>
       </c>
       <c r="J126" s="16" t="inlineStr">
         <is>
-          <t>3.23%→1.56%</t>
+          <t>1.73%→0.72%</t>
         </is>
       </c>
       <c r="K126" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>
@@ -4979,18 +4979,18 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (신규)</t>
+          <t>피엠티  (신규)</t>
         </is>
       </c>
       <c r="B129" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>11291225</v>
+        <v>4174217</v>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>0.00%→0.01%</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
@@ -5067,18 +5067,18 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>피엠티  (신규)</t>
+          <t>HT로보틱스  (신규)</t>
         </is>
       </c>
       <c r="B131" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>4174217</v>
+        <v>11291225</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.01%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">

--- a/reports/pdf_rolling5_20261030.xlsx
+++ b/reports/pdf_rolling5_20261030.xlsx
@@ -59,13 +59,13 @@
       <color rgb="000070C0"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,11 +171,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K197"/>
+  <dimension ref="A1:K196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-23 ~ 2026-10-30  (최근 5거래일)  ·  캡처 18/23  ·  대기: TIGER, RISE, RISE, DS, RISE</t>
+          <t>최근 5거래일 변화  ·  2026-10-23 ~ 2026-10-30  (최근 5거래일)  ·  캡처 17/23  ·  대기: SOL, TIGER, RISE, RISE, DS, RISE</t>
         </is>
       </c>
     </row>
@@ -1945,18 +1945,18 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍  (신규)</t>
+          <t>에이치브이엠  (신규)</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>2634651343</v>
+        <v>4468902278</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>0.00%→2.11%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1989,18 +1989,18 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>티에프이  (신규)</t>
+          <t>한양디지텍  (신규)</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>5716192914</v>
+        <v>2634651343</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.70%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -2033,18 +2033,18 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>에이치브이엠  (신규)</t>
+          <t>티에프이  (신규)</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>4468902278</v>
+        <v>5716192914</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.11%</t>
+          <t>0.00%→2.70%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -2954,23 +2954,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>806989840</v>
+        <v>1850925633</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>1.12%→1.71%</t>
+          <t>1.01%→2.23%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>285→370</t>
+          <t>125→210</t>
         </is>
       </c>
       <c r="G68" s="17" t="n"/>
@@ -2982,23 +2982,23 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B69" s="11" t="n">
         <v>85</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>1850925633</v>
+        <v>806989840</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>1.01%→2.23%</t>
+          <t>1.12%→1.71%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>125→210</t>
+          <t>285→370</t>
         </is>
       </c>
       <c r="G69" s="17" t="n"/>
@@ -4715,23 +4715,23 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>태웅  (신규)</t>
+          <t>제이에스링크</t>
         </is>
       </c>
       <c r="B123" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>238454513</v>
+        <v>193996892</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.80%</t>
+          <t>0.32%→1.00%</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>0→24</t>
+          <t>13→37</t>
         </is>
       </c>
       <c r="G123" s="14" t="inlineStr">
@@ -4759,23 +4759,23 @@
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>제이에스링크</t>
+          <t>태웅  (신규)</t>
         </is>
       </c>
       <c r="B124" s="11" t="n">
         <v>24</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>193996892</v>
+        <v>238454513</v>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>0.32%→1.00%</t>
+          <t>0.00%→0.80%</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>13→37</t>
+          <t>0→24</t>
         </is>
       </c>
       <c r="G124" s="14" t="inlineStr">
@@ -4824,23 +4824,23 @@
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H125" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I125" s="15" t="n">
-        <v>-411106695</v>
+        <v>-231129110</v>
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
-          <t>3.23%→1.56%</t>
+          <t>1.73%→0.72%</t>
         </is>
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
-          <t>32→17</t>
+          <t>29→14</t>
         </is>
       </c>
     </row>
@@ -4868,23 +4868,23 @@
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H126" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I126" s="15" t="n">
-        <v>-231129110</v>
+        <v>-411106695</v>
       </c>
       <c r="J126" s="16" t="inlineStr">
         <is>
-          <t>1.73%→0.72%</t>
+          <t>3.23%→1.56%</t>
         </is>
       </c>
       <c r="K126" s="13" t="inlineStr">
         <is>
-          <t>29→14</t>
+          <t>32→17</t>
         </is>
       </c>
     </row>
@@ -4912,23 +4912,23 @@
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H127" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I127" s="15" t="n">
-        <v>-82558139</v>
+        <v>-95356545</v>
       </c>
       <c r="J127" s="16" t="inlineStr">
         <is>
-          <t>1.13%→0.66%</t>
+          <t>1.07%→0.64%</t>
         </is>
       </c>
       <c r="K127" s="13" t="inlineStr">
         <is>
-          <t>34→24</t>
+          <t>30→20</t>
         </is>
       </c>
     </row>
@@ -4956,23 +4956,23 @@
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="H128" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I128" s="15" t="n">
-        <v>-95356545</v>
+        <v>-82558139</v>
       </c>
       <c r="J128" s="16" t="inlineStr">
         <is>
-          <t>1.07%→0.64%</t>
+          <t>1.13%→0.66%</t>
         </is>
       </c>
       <c r="K128" s="13" t="inlineStr">
         <is>
-          <t>30→20</t>
+          <t>34→24</t>
         </is>
       </c>
     </row>
@@ -5023,23 +5023,23 @@
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>HT로보틱스  (신규)</t>
         </is>
       </c>
       <c r="B130" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>47930873</v>
+        <v>11291225</v>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.07%</t>
+          <t>0.00%→0.04%</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>0→3</t>
         </is>
       </c>
       <c r="G130" s="14" t="inlineStr">
@@ -5067,23 +5067,23 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>HT로보틱스  (신규)</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B131" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>11291225</v>
+        <v>47930873</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.04%</t>
+          <t>1.05%→1.07%</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>0→3</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G131" s="14" t="inlineStr">
@@ -5137,834 +5137,855 @@
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,113억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="n"/>
-      <c r="C134" s="4" t="n"/>
-      <c r="D134" s="4" t="n"/>
-      <c r="E134" s="4" t="n"/>
-      <c r="F134" s="4" t="n"/>
-      <c r="G134" s="4" t="n"/>
-      <c r="H134" s="4" t="n"/>
-      <c r="I134" s="4" t="n"/>
-      <c r="J134" s="4" t="n"/>
-      <c r="K134" s="4" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="18" t="inlineStr">
+      <c r="A134" s="18" t="inlineStr">
+        <is>
+          <t>■ SOL 코리아메가테크액티브  (신한)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B134" s="19" t="n"/>
+      <c r="C134" s="19" t="n"/>
+      <c r="D134" s="19" t="n"/>
+      <c r="E134" s="19" t="n"/>
+      <c r="F134" s="19" t="n"/>
+      <c r="G134" s="19" t="n"/>
+      <c r="H134" s="19" t="n"/>
+      <c r="I134" s="19" t="n"/>
+      <c r="J134" s="19" t="n"/>
+      <c r="K134" s="19" t="n"/>
+    </row>
+    <row r="136" ht="19" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="n"/>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="n"/>
+      <c r="J136" s="4" t="n"/>
+      <c r="K136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="19" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="n"/>
-      <c r="C137" s="4" t="n"/>
-      <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="n"/>
-      <c r="G137" s="4" t="n"/>
-      <c r="H137" s="4" t="n"/>
-      <c r="I137" s="4" t="n"/>
-      <c r="J137" s="4" t="n"/>
-      <c r="K137" s="4" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="19" customHeight="1">
-      <c r="A140" s="19" t="inlineStr">
+    <row r="139" ht="19" customHeight="1">
+      <c r="A139" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 코리아테크액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B140" s="20" t="n"/>
-      <c r="C140" s="20" t="n"/>
-      <c r="D140" s="20" t="n"/>
-      <c r="E140" s="20" t="n"/>
-      <c r="F140" s="20" t="n"/>
-      <c r="G140" s="20" t="n"/>
-      <c r="H140" s="20" t="n"/>
-      <c r="I140" s="20" t="n"/>
-      <c r="J140" s="20" t="n"/>
-      <c r="K140" s="20" t="n"/>
-    </row>
-    <row r="142" ht="19" customHeight="1">
-      <c r="A142" s="19" t="inlineStr">
+      <c r="B139" s="19" t="n"/>
+      <c r="C139" s="19" t="n"/>
+      <c r="D139" s="19" t="n"/>
+      <c r="E139" s="19" t="n"/>
+      <c r="F139" s="19" t="n"/>
+      <c r="G139" s="19" t="n"/>
+      <c r="H139" s="19" t="n"/>
+      <c r="I139" s="19" t="n"/>
+      <c r="J139" s="19" t="n"/>
+      <c r="K139" s="19" t="n"/>
+    </row>
+    <row r="141" ht="19" customHeight="1">
+      <c r="A141" s="18" t="inlineStr">
         <is>
           <t>■ RISE 비메모리반도체액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B142" s="20" t="n"/>
-      <c r="C142" s="20" t="n"/>
-      <c r="D142" s="20" t="n"/>
-      <c r="E142" s="20" t="n"/>
-      <c r="F142" s="20" t="n"/>
-      <c r="G142" s="20" t="n"/>
-      <c r="H142" s="20" t="n"/>
-      <c r="I142" s="20" t="n"/>
-      <c r="J142" s="20" t="n"/>
-      <c r="K142" s="20" t="n"/>
-    </row>
-    <row r="144" ht="19" customHeight="1">
-      <c r="A144" s="3" t="inlineStr">
+      <c r="B141" s="19" t="n"/>
+      <c r="C141" s="19" t="n"/>
+      <c r="D141" s="19" t="n"/>
+      <c r="E141" s="19" t="n"/>
+      <c r="F141" s="19" t="n"/>
+      <c r="G141" s="19" t="n"/>
+      <c r="H141" s="19" t="n"/>
+      <c r="I141" s="19" t="n"/>
+      <c r="J141" s="19" t="n"/>
+      <c r="K141" s="19" t="n"/>
+    </row>
+    <row r="143" ht="19" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 808억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B144" s="4" t="n"/>
-      <c r="C144" s="4" t="n"/>
-      <c r="D144" s="4" t="n"/>
-      <c r="E144" s="4" t="n"/>
-      <c r="F144" s="4" t="n"/>
-      <c r="G144" s="4" t="n"/>
-      <c r="H144" s="4" t="n"/>
-      <c r="I144" s="4" t="n"/>
-      <c r="J144" s="4" t="n"/>
-      <c r="K144" s="4" t="n"/>
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="n"/>
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="n"/>
+      <c r="J143" s="4" t="n"/>
+      <c r="K143" s="4" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+      <c r="E144" s="6" t="n"/>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="n"/>
+      <c r="I144" s="8" t="n"/>
+      <c r="J144" s="8" t="n"/>
+      <c r="K144" s="8" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="n"/>
-      <c r="C145" s="6" t="n"/>
-      <c r="D145" s="6" t="n"/>
-      <c r="E145" s="6" t="n"/>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H145" s="8" t="n"/>
-      <c r="I145" s="8" t="n"/>
-      <c r="J145" s="8" t="n"/>
-      <c r="K145" s="8" t="n"/>
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B146" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C146" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D146" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E146" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G146" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H146" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I146" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J146" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K146" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>767188000</v>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>4.41%→5.30%</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>209→255</t>
+        </is>
+      </c>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="n">
+        <v>-1215</v>
+      </c>
+      <c r="I146" s="15" t="n">
+        <v>-772132500</v>
+      </c>
+      <c r="J146" s="16" t="inlineStr">
+        <is>
+          <t>3.04%→1.69%</t>
+        </is>
+      </c>
+      <c r="K146" s="13" t="inlineStr">
+        <is>
+          <t>3,349→2,134</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B147" s="11" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C147" s="11" t="n">
-        <v>767188000</v>
+        <v>881826000</v>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>4.41%→5.30%</t>
+          <t>2.98%→4.25%</t>
         </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>209→255</t>
+          <t>63→85</t>
         </is>
       </c>
       <c r="G147" s="14" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="H147" s="15" t="n">
-        <v>-1215</v>
+        <v>-117</v>
       </c>
       <c r="I147" s="15" t="n">
-        <v>-772132500</v>
+        <v>-748975500</v>
       </c>
       <c r="J147" s="16" t="inlineStr">
         <is>
-          <t>3.04%→1.69%</t>
+          <t>1.92%→0.86%</t>
         </is>
       </c>
       <c r="K147" s="13" t="inlineStr">
         <is>
-          <t>3,349→2,134</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="10" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="B148" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C148" s="11" t="n">
-        <v>881826000</v>
-      </c>
-      <c r="D148" s="12" t="inlineStr">
-        <is>
-          <t>2.98%→4.25%</t>
-        </is>
-      </c>
-      <c r="E148" s="13" t="inlineStr">
-        <is>
-          <t>63→85</t>
-        </is>
-      </c>
-      <c r="G148" s="14" t="inlineStr">
-        <is>
-          <t>삼성에스디에스</t>
-        </is>
-      </c>
-      <c r="H148" s="15" t="n">
-        <v>-117</v>
-      </c>
-      <c r="I148" s="15" t="n">
-        <v>-748975500</v>
-      </c>
-      <c r="J148" s="16" t="inlineStr">
-        <is>
-          <t>1.92%→0.86%</t>
-        </is>
-      </c>
-      <c r="K148" s="13" t="inlineStr">
-        <is>
           <t>225→108</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="19" customHeight="1">
-      <c r="A150" s="3" t="inlineStr">
+    <row r="149" ht="19" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
         <is>
           <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 366억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 11종목  /  매도 15종목</t>
         </is>
       </c>
-      <c r="B150" s="4" t="n"/>
-      <c r="C150" s="4" t="n"/>
-      <c r="D150" s="4" t="n"/>
-      <c r="E150" s="4" t="n"/>
-      <c r="F150" s="4" t="n"/>
-      <c r="G150" s="4" t="n"/>
-      <c r="H150" s="4" t="n"/>
-      <c r="I150" s="4" t="n"/>
-      <c r="J150" s="4" t="n"/>
-      <c r="K150" s="4" t="n"/>
+      <c r="B149" s="4" t="n"/>
+      <c r="C149" s="4" t="n"/>
+      <c r="D149" s="4" t="n"/>
+      <c r="E149" s="4" t="n"/>
+      <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="n"/>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="n"/>
+      <c r="J149" s="4" t="n"/>
+      <c r="K149" s="4" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="n"/>
+      <c r="C150" s="6" t="n"/>
+      <c r="D150" s="6" t="n"/>
+      <c r="E150" s="6" t="n"/>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="n"/>
+      <c r="I150" s="8" t="n"/>
+      <c r="J150" s="8" t="n"/>
+      <c r="K150" s="8" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="n"/>
-      <c r="C151" s="6" t="n"/>
-      <c r="D151" s="6" t="n"/>
-      <c r="E151" s="6" t="n"/>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H151" s="8" t="n"/>
-      <c r="I151" s="8" t="n"/>
-      <c r="J151" s="8" t="n"/>
-      <c r="K151" s="8" t="n"/>
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K151" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D152" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E152" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H152" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I152" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J152" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K152" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스  (신규)</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="n">
+        <v>1174</v>
+      </c>
+      <c r="C152" s="11" t="n">
+        <v>577889760</v>
+      </c>
+      <c r="D152" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.59%</t>
+        </is>
+      </c>
+      <c r="E152" s="13" t="inlineStr">
+        <is>
+          <t>0→1,174</t>
+        </is>
+      </c>
+      <c r="G152" s="14" t="inlineStr">
+        <is>
+          <t>솔루엠  (편출)</t>
+        </is>
+      </c>
+      <c r="H152" s="15" t="n">
+        <v>-574</v>
+      </c>
+      <c r="I152" s="15" t="n">
+        <v>-243972960</v>
+      </c>
+      <c r="J152" s="16" t="inlineStr">
+        <is>
+          <t>0.71%→0.00%</t>
+        </is>
+      </c>
+      <c r="K152" s="13" t="inlineStr">
+        <is>
+          <t>574→0</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>샘씨엔에스  (신규)</t>
+          <t>한화비전  (신규)</t>
         </is>
       </c>
       <c r="B153" s="11" t="n">
-        <v>1174</v>
+        <v>997</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>577889760</v>
+        <v>1370675600</v>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.59%</t>
+          <t>0.00%→3.78%</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>0→1,174</t>
+          <t>0→997</t>
         </is>
       </c>
       <c r="G153" s="14" t="inlineStr">
         <is>
-          <t>솔루엠  (편출)</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H153" s="15" t="n">
-        <v>-574</v>
+        <v>-541</v>
       </c>
       <c r="I153" s="15" t="n">
-        <v>-243972960</v>
+        <v>-691506200</v>
       </c>
       <c r="J153" s="16" t="inlineStr">
         <is>
-          <t>0.71%→0.00%</t>
+          <t>3.39%→1.13%</t>
         </is>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
-          <t>574→0</t>
+          <t>861→320</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>한화비전  (신규)</t>
+          <t>인텍플러스  (신규)</t>
         </is>
       </c>
       <c r="B154" s="11" t="n">
-        <v>997</v>
+        <v>324</v>
       </c>
       <c r="C154" s="11" t="n">
-        <v>1370675600</v>
+        <v>562464000</v>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>0.00%→3.78%</t>
+          <t>0.00%→1.55%</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>0→997</t>
+          <t>0→324</t>
         </is>
       </c>
       <c r="G154" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>두산퓨얼셀  (편출)</t>
         </is>
       </c>
       <c r="H154" s="15" t="n">
-        <v>-541</v>
+        <v>-513</v>
       </c>
       <c r="I154" s="15" t="n">
-        <v>-691506200</v>
+        <v>-480475800</v>
       </c>
       <c r="J154" s="16" t="inlineStr">
         <is>
-          <t>3.39%→1.13%</t>
+          <t>1.40%→0.00%</t>
         </is>
       </c>
       <c r="K154" s="13" t="inlineStr">
         <is>
-          <t>861→320</t>
+          <t>513→0</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스  (신규)</t>
+          <t>ISC  (신규)</t>
         </is>
       </c>
       <c r="B155" s="11" t="n">
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>562464000</v>
+        <v>767844000</v>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.55%</t>
+          <t>0.00%→2.12%</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>0→324</t>
+          <t>0→165</t>
         </is>
       </c>
       <c r="G155" s="14" t="inlineStr">
         <is>
-          <t>두산퓨얼셀  (편출)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="H155" s="15" t="n">
-        <v>-513</v>
+        <v>-473</v>
       </c>
       <c r="I155" s="15" t="n">
-        <v>-480475800</v>
+        <v>-750934800</v>
       </c>
       <c r="J155" s="16" t="inlineStr">
         <is>
-          <t>1.40%→0.00%</t>
+          <t>2.95%→0.50%</t>
         </is>
       </c>
       <c r="K155" s="13" t="inlineStr">
         <is>
-          <t>513→0</t>
+          <t>588→115</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="10" t="inlineStr">
         <is>
-          <t>ISC  (신규)</t>
+          <t>에코프로에이치엔  (신규)</t>
         </is>
       </c>
       <c r="B156" s="11" t="n">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>767844000</v>
+        <v>73038000</v>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.12%</t>
+          <t>0.00%→0.20%</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>0→165</t>
+          <t>0→111</t>
         </is>
       </c>
       <c r="G156" s="14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>현대건설  (편출)</t>
         </is>
       </c>
       <c r="H156" s="15" t="n">
-        <v>-473</v>
+        <v>-216</v>
       </c>
       <c r="I156" s="15" t="n">
-        <v>-750934800</v>
+        <v>-562464000</v>
       </c>
       <c r="J156" s="16" t="inlineStr">
         <is>
-          <t>2.95%→0.50%</t>
+          <t>1.64%→0.00%</t>
         </is>
       </c>
       <c r="K156" s="13" t="inlineStr">
         <is>
-          <t>588→115</t>
+          <t>216→0</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔  (신규)</t>
+          <t>케이씨텍</t>
         </is>
       </c>
       <c r="B157" s="11" t="n">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="C157" s="11" t="n">
-        <v>73038000</v>
+        <v>163800000</v>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.20%</t>
+          <t>4.80%→5.29%</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>0→111</t>
+          <t>644→704</t>
         </is>
       </c>
       <c r="G157" s="14" t="inlineStr">
         <is>
-          <t>현대건설  (편출)</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="H157" s="15" t="n">
-        <v>-216</v>
+        <v>-191</v>
       </c>
       <c r="I157" s="15" t="n">
-        <v>-562464000</v>
+        <v>-277026400</v>
       </c>
       <c r="J157" s="16" t="inlineStr">
         <is>
-          <t>1.64%→0.00%</t>
+          <t>1.54%→0.84%</t>
         </is>
       </c>
       <c r="K157" s="13" t="inlineStr">
         <is>
-          <t>216→0</t>
+          <t>401→210</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="10" t="inlineStr">
         <is>
-          <t>케이씨텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B158" s="11" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>163800000</v>
+        <v>1367296000</v>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>4.80%→5.29%</t>
+          <t>5.88%→10.71%</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>644→704</t>
+          <t>59→91</t>
         </is>
       </c>
       <c r="G158" s="14" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>비에이치아이  (편출)</t>
         </is>
       </c>
       <c r="H158" s="15" t="n">
-        <v>-191</v>
+        <v>-157</v>
       </c>
       <c r="I158" s="15" t="n">
-        <v>-277026400</v>
+        <v>-201776400</v>
       </c>
       <c r="J158" s="16" t="inlineStr">
         <is>
-          <t>1.54%→0.84%</t>
+          <t>0.59%→0.00%</t>
         </is>
       </c>
       <c r="K158" s="13" t="inlineStr">
         <is>
-          <t>401→210</t>
+          <t>157→0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B159" s="11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C159" s="11" t="n">
-        <v>1367296000</v>
+        <v>168565600</v>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>5.88%→10.71%</t>
+          <t>5.37%→6.32%</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>59→91</t>
+          <t>391→422</t>
         </is>
       </c>
       <c r="G159" s="14" t="inlineStr">
         <is>
-          <t>비에이치아이  (편출)</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="H159" s="15" t="n">
-        <v>-157</v>
+        <v>-138</v>
       </c>
       <c r="I159" s="15" t="n">
-        <v>-201776400</v>
+        <v>-896448000</v>
       </c>
       <c r="J159" s="16" t="inlineStr">
         <is>
-          <t>0.59%→0.00%</t>
+          <t>8.52%→6.26%</t>
         </is>
       </c>
       <c r="K159" s="13" t="inlineStr">
         <is>
-          <t>157→0</t>
+          <t>488→350</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B160" s="11" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>168565600</v>
+        <v>118431600</v>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>5.37%→6.32%</t>
+          <t>5.23%→5.77%</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>391→422</t>
+          <t>384→407</t>
         </is>
       </c>
       <c r="G160" s="14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK텔레콤  (편출)</t>
         </is>
       </c>
       <c r="H160" s="15" t="n">
-        <v>-138</v>
+        <v>-77</v>
       </c>
       <c r="I160" s="15" t="n">
-        <v>-896448000</v>
+        <v>-164287200</v>
       </c>
       <c r="J160" s="16" t="inlineStr">
         <is>
-          <t>8.52%→6.26%</t>
+          <t>0.48%→0.00%</t>
         </is>
       </c>
       <c r="K160" s="13" t="inlineStr">
         <is>
-          <t>488→350</t>
+          <t>77→0</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B161" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C161" s="11" t="n">
-        <v>118431600</v>
+        <v>331408000</v>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>5.23%→5.77%</t>
+          <t>5.59%→6.47%</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>384→407</t>
+          <t>134→156</t>
         </is>
       </c>
       <c r="G161" s="14" t="inlineStr">
         <is>
-          <t>SK텔레콤  (편출)</t>
+          <t>DB하이텍  (편출)</t>
         </is>
       </c>
       <c r="H161" s="15" t="n">
-        <v>-77</v>
+        <v>-69</v>
       </c>
       <c r="I161" s="15" t="n">
-        <v>-164287200</v>
+        <v>-191074800</v>
       </c>
       <c r="J161" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.00%</t>
+          <t>0.56%→0.00%</t>
         </is>
       </c>
       <c r="K161" s="13" t="inlineStr">
         <is>
-          <t>77→0</t>
+          <t>69→0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="B162" s="11" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>331408000</v>
+        <v>108612000</v>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>5.59%→6.47%</t>
+          <t>1.12%→1.50%</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>134→156</t>
+          <t>12→15</t>
         </is>
       </c>
       <c r="G162" s="14" t="inlineStr">
         <is>
-          <t>DB하이텍  (편출)</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H162" s="15" t="n">
-        <v>-69</v>
+        <v>-43</v>
       </c>
       <c r="I162" s="15" t="n">
-        <v>-191074800</v>
+        <v>-144841200</v>
       </c>
       <c r="J162" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.00%</t>
+          <t>3.04%→2.55%</t>
         </is>
       </c>
       <c r="K162" s="13" t="inlineStr">
         <is>
-          <t>69→0</t>
+          <t>318→275</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="10" t="inlineStr">
-        <is>
-          <t>삼성전기</t>
-        </is>
-      </c>
-      <c r="B163" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C163" s="11" t="n">
-        <v>108612000</v>
-      </c>
-      <c r="D163" s="12" t="inlineStr">
-        <is>
-          <t>1.12%→1.50%</t>
-        </is>
-      </c>
-      <c r="E163" s="13" t="inlineStr">
-        <is>
-          <t>12→15</t>
-        </is>
-      </c>
+      <c r="A163" s="17" t="n"/>
+      <c r="B163" s="17" t="n"/>
+      <c r="C163" s="17" t="n"/>
+      <c r="D163" s="17" t="n"/>
+      <c r="E163" s="17" t="n"/>
       <c r="G163" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="H163" s="15" t="n">
-        <v>-43</v>
+        <v>-30</v>
       </c>
       <c r="I163" s="15" t="n">
-        <v>-144841200</v>
+        <v>-299040000</v>
       </c>
       <c r="J163" s="16" t="inlineStr">
         <is>
-          <t>3.04%→2.55%</t>
+          <t>4.19%→2.80%</t>
         </is>
       </c>
       <c r="K163" s="13" t="inlineStr">
         <is>
-          <t>318→275</t>
+          <t>132→102</t>
         </is>
       </c>
     </row>
@@ -5976,23 +5997,23 @@
       <c r="E164" s="17" t="n"/>
       <c r="G164" s="14" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="H164" s="15" t="n">
-        <v>-30</v>
+        <v>-24</v>
       </c>
       <c r="I164" s="15" t="n">
-        <v>-299040000</v>
+        <v>-18480000</v>
       </c>
       <c r="J164" s="16" t="inlineStr">
         <is>
-          <t>4.19%→2.80%</t>
+          <t>3.01%→2.77%</t>
         </is>
       </c>
       <c r="K164" s="13" t="inlineStr">
         <is>
-          <t>132→102</t>
+          <t>1,328→1,304</t>
         </is>
       </c>
     </row>
@@ -6004,23 +6025,23 @@
       <c r="E165" s="17" t="n"/>
       <c r="G165" s="14" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>두산  (편출)</t>
         </is>
       </c>
       <c r="H165" s="15" t="n">
-        <v>-24</v>
+        <v>-19</v>
       </c>
       <c r="I165" s="15" t="n">
-        <v>-18480000</v>
+        <v>-536788000</v>
       </c>
       <c r="J165" s="16" t="inlineStr">
         <is>
-          <t>3.01%→2.77%</t>
+          <t>1.56%→0.00%</t>
         </is>
       </c>
       <c r="K165" s="13" t="inlineStr">
         <is>
-          <t>1,328→1,304</t>
+          <t>19→0</t>
         </is>
       </c>
     </row>
@@ -6032,207 +6053,207 @@
       <c r="E166" s="17" t="n"/>
       <c r="G166" s="14" t="inlineStr">
         <is>
-          <t>두산  (편출)</t>
+          <t>HD현대일렉트릭  (편출)</t>
         </is>
       </c>
       <c r="H166" s="15" t="n">
-        <v>-19</v>
+        <v>-13</v>
       </c>
       <c r="I166" s="15" t="n">
-        <v>-536788000</v>
+        <v>-178360000</v>
       </c>
       <c r="J166" s="16" t="inlineStr">
         <is>
-          <t>1.56%→0.00%</t>
+          <t>0.52%→0.00%</t>
         </is>
       </c>
       <c r="K166" s="13" t="inlineStr">
         <is>
-          <t>19→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="17" t="n"/>
-      <c r="B167" s="17" t="n"/>
-      <c r="C167" s="17" t="n"/>
-      <c r="D167" s="17" t="n"/>
-      <c r="E167" s="17" t="n"/>
-      <c r="G167" s="14" t="inlineStr">
-        <is>
-          <t>HD현대일렉트릭  (편출)</t>
-        </is>
-      </c>
-      <c r="H167" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I167" s="15" t="n">
-        <v>-178360000</v>
-      </c>
-      <c r="J167" s="16" t="inlineStr">
-        <is>
-          <t>0.52%→0.00%</t>
-        </is>
-      </c>
-      <c r="K167" s="13" t="inlineStr">
-        <is>
           <t>13→0</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="19" customHeight="1">
-      <c r="A169" s="3" t="inlineStr">
+    <row r="168" ht="19" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 540억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
-      <c r="B169" s="4" t="n"/>
-      <c r="C169" s="4" t="n"/>
-      <c r="D169" s="4" t="n"/>
-      <c r="E169" s="4" t="n"/>
-      <c r="F169" s="4" t="n"/>
-      <c r="G169" s="4" t="n"/>
-      <c r="H169" s="4" t="n"/>
-      <c r="I169" s="4" t="n"/>
-      <c r="J169" s="4" t="n"/>
-      <c r="K169" s="4" t="n"/>
+      <c r="B168" s="4" t="n"/>
+      <c r="C168" s="4" t="n"/>
+      <c r="D168" s="4" t="n"/>
+      <c r="E168" s="4" t="n"/>
+      <c r="F168" s="4" t="n"/>
+      <c r="G168" s="4" t="n"/>
+      <c r="H168" s="4" t="n"/>
+      <c r="I168" s="4" t="n"/>
+      <c r="J168" s="4" t="n"/>
+      <c r="K168" s="4" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="n"/>
+      <c r="C169" s="6" t="n"/>
+      <c r="D169" s="6" t="n"/>
+      <c r="E169" s="6" t="n"/>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H169" s="8" t="n"/>
+      <c r="I169" s="8" t="n"/>
+      <c r="J169" s="8" t="n"/>
+      <c r="K169" s="8" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="n"/>
-      <c r="C170" s="6" t="n"/>
-      <c r="D170" s="6" t="n"/>
-      <c r="E170" s="6" t="n"/>
-      <c r="G170" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H170" s="8" t="n"/>
-      <c r="I170" s="8" t="n"/>
-      <c r="J170" s="8" t="n"/>
-      <c r="K170" s="8" t="n"/>
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E170" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I170" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K170" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B171" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C171" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D171" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E171" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G171" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H171" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I171" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J171" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K171" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A171" s="10" t="inlineStr">
+        <is>
+          <t>디케이티  (신규)</t>
+        </is>
+      </c>
+      <c r="B171" s="11" t="n">
+        <v>298</v>
+      </c>
+      <c r="C171" s="11" t="n">
+        <v>727120000</v>
+      </c>
+      <c r="D171" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.34%</t>
+        </is>
+      </c>
+      <c r="E171" s="13" t="inlineStr">
+        <is>
+          <t>0→298</t>
+        </is>
+      </c>
+      <c r="G171" s="14" t="inlineStr">
+        <is>
+          <t>기가비스  (편출)</t>
+        </is>
+      </c>
+      <c r="H171" s="15" t="n">
+        <v>-275</v>
+      </c>
+      <c r="I171" s="15" t="n">
+        <v>-2871000000</v>
+      </c>
+      <c r="J171" s="16" t="inlineStr">
+        <is>
+          <t>5.23%→0.00%</t>
+        </is>
+      </c>
+      <c r="K171" s="13" t="inlineStr">
+        <is>
+          <t>275→0</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
         <is>
-          <t>디케이티  (신규)</t>
+          <t>GST  (신규)</t>
         </is>
       </c>
       <c r="B172" s="11" t="n">
-        <v>298</v>
+        <v>154</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>727120000</v>
+        <v>681450000</v>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.34%</t>
+          <t>0.00%→1.25%</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>0→298</t>
-        </is>
-      </c>
-      <c r="G172" s="14" t="inlineStr">
-        <is>
-          <t>기가비스  (편출)</t>
-        </is>
-      </c>
-      <c r="H172" s="15" t="n">
-        <v>-275</v>
-      </c>
-      <c r="I172" s="15" t="n">
-        <v>-2871000000</v>
-      </c>
-      <c r="J172" s="16" t="inlineStr">
-        <is>
-          <t>5.23%→0.00%</t>
-        </is>
-      </c>
-      <c r="K172" s="13" t="inlineStr">
-        <is>
-          <t>275→0</t>
-        </is>
-      </c>
+          <t>0→154</t>
+        </is>
+      </c>
+      <c r="G172" s="17" t="n"/>
+      <c r="H172" s="17" t="n"/>
+      <c r="I172" s="17" t="n"/>
+      <c r="J172" s="17" t="n"/>
+      <c r="K172" s="17" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>GST  (신규)</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B173" s="11" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>681450000</v>
+        <v>453330000</v>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.25%</t>
+          <t>0.95%→1.79%</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>0→154</t>
+          <t>168→314</t>
         </is>
       </c>
       <c r="G173" s="17" t="n"/>
@@ -6244,23 +6265,23 @@
     <row r="174">
       <c r="A174" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="B174" s="11" t="n">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="C174" s="11" t="n">
-        <v>453330000</v>
+        <v>451935000</v>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>0.95%→1.79%</t>
+          <t>1.00%→1.84%</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>168→314</t>
+          <t>147→268</t>
         </is>
       </c>
       <c r="G174" s="17" t="n"/>
@@ -6272,23 +6293,23 @@
     <row r="175">
       <c r="A175" s="10" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B175" s="11" t="n">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="C175" s="11" t="n">
-        <v>451935000</v>
+        <v>602020000</v>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.84%</t>
+          <t>6.12%→7.28%</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>147→268</t>
+          <t>173→204</t>
         </is>
       </c>
       <c r="G175" s="17" t="n"/>
@@ -6297,392 +6318,363 @@
       <c r="J175" s="17" t="n"/>
       <c r="K175" s="17" t="n"/>
     </row>
-    <row r="176">
-      <c r="A176" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="B176" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="C176" s="11" t="n">
-        <v>602020000</v>
-      </c>
-      <c r="D176" s="12" t="inlineStr">
-        <is>
-          <t>6.12%→7.28%</t>
-        </is>
-      </c>
-      <c r="E176" s="13" t="inlineStr">
-        <is>
-          <t>173→204</t>
-        </is>
-      </c>
-      <c r="G176" s="17" t="n"/>
-      <c r="H176" s="17" t="n"/>
-      <c r="I176" s="17" t="n"/>
-      <c r="J176" s="17" t="n"/>
-      <c r="K176" s="17" t="n"/>
-    </row>
-    <row r="178" ht="19" customHeight="1">
-      <c r="A178" s="19" t="inlineStr">
+    <row r="177" ht="19" customHeight="1">
+      <c r="A177" s="18" t="inlineStr">
         <is>
           <t>■ RISE 반도체소부장액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B178" s="20" t="n"/>
-      <c r="C178" s="20" t="n"/>
-      <c r="D178" s="20" t="n"/>
-      <c r="E178" s="20" t="n"/>
-      <c r="F178" s="20" t="n"/>
-      <c r="G178" s="20" t="n"/>
-      <c r="H178" s="20" t="n"/>
-      <c r="I178" s="20" t="n"/>
-      <c r="J178" s="20" t="n"/>
-      <c r="K178" s="20" t="n"/>
-    </row>
-    <row r="180" ht="19" customHeight="1">
-      <c r="A180" s="19" t="inlineStr">
+      <c r="B177" s="19" t="n"/>
+      <c r="C177" s="19" t="n"/>
+      <c r="D177" s="19" t="n"/>
+      <c r="E177" s="19" t="n"/>
+      <c r="F177" s="19" t="n"/>
+      <c r="G177" s="19" t="n"/>
+      <c r="H177" s="19" t="n"/>
+      <c r="I177" s="19" t="n"/>
+      <c r="J177" s="19" t="n"/>
+      <c r="K177" s="19" t="n"/>
+    </row>
+    <row r="179" ht="19" customHeight="1">
+      <c r="A179" s="18" t="inlineStr">
         <is>
           <t>■ DS AI반도체액티브  (DS)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B180" s="20" t="n"/>
-      <c r="C180" s="20" t="n"/>
-      <c r="D180" s="20" t="n"/>
-      <c r="E180" s="20" t="n"/>
-      <c r="F180" s="20" t="n"/>
-      <c r="G180" s="20" t="n"/>
-      <c r="H180" s="20" t="n"/>
-      <c r="I180" s="20" t="n"/>
-      <c r="J180" s="20" t="n"/>
-      <c r="K180" s="20" t="n"/>
-    </row>
-    <row r="182" ht="19" customHeight="1">
-      <c r="A182" s="19" t="inlineStr">
+      <c r="B179" s="19" t="n"/>
+      <c r="C179" s="19" t="n"/>
+      <c r="D179" s="19" t="n"/>
+      <c r="E179" s="19" t="n"/>
+      <c r="F179" s="19" t="n"/>
+      <c r="G179" s="19" t="n"/>
+      <c r="H179" s="19" t="n"/>
+      <c r="I179" s="19" t="n"/>
+      <c r="J179" s="19" t="n"/>
+      <c r="K179" s="19" t="n"/>
+    </row>
+    <row r="181" ht="19" customHeight="1">
+      <c r="A181" s="18" t="inlineStr">
         <is>
           <t>■ RISE 2차전지액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B182" s="20" t="n"/>
-      <c r="C182" s="20" t="n"/>
-      <c r="D182" s="20" t="n"/>
-      <c r="E182" s="20" t="n"/>
-      <c r="F182" s="20" t="n"/>
-      <c r="G182" s="20" t="n"/>
-      <c r="H182" s="20" t="n"/>
-      <c r="I182" s="20" t="n"/>
-      <c r="J182" s="20" t="n"/>
-      <c r="K182" s="20" t="n"/>
-    </row>
-    <row r="184" ht="19" customHeight="1">
-      <c r="A184" s="3" t="inlineStr">
+      <c r="B181" s="19" t="n"/>
+      <c r="C181" s="19" t="n"/>
+      <c r="D181" s="19" t="n"/>
+      <c r="E181" s="19" t="n"/>
+      <c r="F181" s="19" t="n"/>
+      <c r="G181" s="19" t="n"/>
+      <c r="H181" s="19" t="n"/>
+      <c r="I181" s="19" t="n"/>
+      <c r="J181" s="19" t="n"/>
+      <c r="K181" s="19" t="n"/>
+    </row>
+    <row r="183" ht="19" customHeight="1">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 281억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B184" s="4" t="n"/>
-      <c r="C184" s="4" t="n"/>
-      <c r="D184" s="4" t="n"/>
-      <c r="E184" s="4" t="n"/>
-      <c r="F184" s="4" t="n"/>
-      <c r="G184" s="4" t="n"/>
-      <c r="H184" s="4" t="n"/>
-      <c r="I184" s="4" t="n"/>
-      <c r="J184" s="4" t="n"/>
-      <c r="K184" s="4" t="n"/>
+      <c r="B183" s="4" t="n"/>
+      <c r="C183" s="4" t="n"/>
+      <c r="D183" s="4" t="n"/>
+      <c r="E183" s="4" t="n"/>
+      <c r="F183" s="4" t="n"/>
+      <c r="G183" s="4" t="n"/>
+      <c r="H183" s="4" t="n"/>
+      <c r="I183" s="4" t="n"/>
+      <c r="J183" s="4" t="n"/>
+      <c r="K183" s="4" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="n"/>
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="6" t="n"/>
+      <c r="E184" s="6" t="n"/>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H184" s="8" t="n"/>
+      <c r="I184" s="8" t="n"/>
+      <c r="J184" s="8" t="n"/>
+      <c r="K184" s="8" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="n"/>
-      <c r="C185" s="6" t="n"/>
-      <c r="D185" s="6" t="n"/>
-      <c r="E185" s="6" t="n"/>
-      <c r="G185" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H185" s="8" t="n"/>
-      <c r="I185" s="8" t="n"/>
-      <c r="J185" s="8" t="n"/>
-      <c r="K185" s="8" t="n"/>
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E185" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G185" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I185" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K185" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B186" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C186" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D186" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E186" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G186" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H186" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I186" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J186" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K186" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A186" s="10" t="inlineStr">
+        <is>
+          <t>에코프로에이치엔</t>
+        </is>
+      </c>
+      <c r="B186" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C186" s="11" t="n">
+        <v>55271980</v>
+      </c>
+      <c r="D186" s="12" t="inlineStr">
+        <is>
+          <t>0.51%→0.73%</t>
+        </is>
+      </c>
+      <c r="E186" s="13" t="inlineStr">
+        <is>
+          <t>112→154</t>
+        </is>
+      </c>
+      <c r="G186" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H186" s="15" t="n">
+        <v>-95</v>
+      </c>
+      <c r="I186" s="15" t="n">
+        <v>-136989951</v>
+      </c>
+      <c r="J186" s="16" t="inlineStr">
+        <is>
+          <t>8.88%→9.20%</t>
+        </is>
+      </c>
+      <c r="K186" s="13" t="inlineStr">
+        <is>
+          <t>1,876→1,781</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="10" t="inlineStr">
         <is>
-          <t>에코프로에이치엔</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B187" s="11" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C187" s="11" t="n">
-        <v>55271980</v>
+        <v>85388770</v>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>0.51%→0.73%</t>
+          <t>6.94%→7.49%</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>112→154</t>
+          <t>752→784</t>
         </is>
       </c>
       <c r="G187" s="14" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>HD현대일렉트릭</t>
         </is>
       </c>
       <c r="H187" s="15" t="n">
-        <v>-95</v>
+        <v>-3</v>
       </c>
       <c r="I187" s="15" t="n">
-        <v>-136989951</v>
+        <v>-74003974</v>
       </c>
       <c r="J187" s="16" t="inlineStr">
         <is>
-          <t>8.88%→9.20%</t>
+          <t>2.20%→1.85%</t>
         </is>
       </c>
       <c r="K187" s="13" t="inlineStr">
         <is>
-          <t>1,876→1,781</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="10" t="inlineStr">
-        <is>
-          <t>한중엔시에스</t>
-        </is>
-      </c>
-      <c r="B188" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="C188" s="11" t="n">
-        <v>85388770</v>
-      </c>
-      <c r="D188" s="12" t="inlineStr">
-        <is>
-          <t>6.94%→7.49%</t>
-        </is>
-      </c>
-      <c r="E188" s="13" t="inlineStr">
-        <is>
-          <t>752→784</t>
-        </is>
-      </c>
-      <c r="G188" s="14" t="inlineStr">
-        <is>
-          <t>HD현대일렉트릭</t>
-        </is>
-      </c>
-      <c r="H188" s="15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I188" s="15" t="n">
-        <v>-74003974</v>
-      </c>
-      <c r="J188" s="16" t="inlineStr">
-        <is>
-          <t>2.20%→1.85%</t>
-        </is>
-      </c>
-      <c r="K188" s="13" t="inlineStr">
-        <is>
           <t>24→21</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="19" customHeight="1">
-      <c r="A190" s="3" t="inlineStr">
+    <row r="189" ht="19" customHeight="1">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 157억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B190" s="4" t="n"/>
-      <c r="C190" s="4" t="n"/>
-      <c r="D190" s="4" t="n"/>
-      <c r="E190" s="4" t="n"/>
-      <c r="F190" s="4" t="n"/>
-      <c r="G190" s="4" t="n"/>
-      <c r="H190" s="4" t="n"/>
-      <c r="I190" s="4" t="n"/>
-      <c r="J190" s="4" t="n"/>
-      <c r="K190" s="4" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="18" t="inlineStr">
+      <c r="B189" s="4" t="n"/>
+      <c r="C189" s="4" t="n"/>
+      <c r="D189" s="4" t="n"/>
+      <c r="E189" s="4" t="n"/>
+      <c r="F189" s="4" t="n"/>
+      <c r="G189" s="4" t="n"/>
+      <c r="H189" s="4" t="n"/>
+      <c r="I189" s="4" t="n"/>
+      <c r="J189" s="4" t="n"/>
+      <c r="K189" s="4" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="19" customHeight="1">
-      <c r="A193" s="3" t="inlineStr">
+    <row r="192" ht="19" customHeight="1">
+      <c r="A192" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 87억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B193" s="4" t="n"/>
-      <c r="C193" s="4" t="n"/>
-      <c r="D193" s="4" t="n"/>
-      <c r="E193" s="4" t="n"/>
-      <c r="F193" s="4" t="n"/>
-      <c r="G193" s="4" t="n"/>
-      <c r="H193" s="4" t="n"/>
-      <c r="I193" s="4" t="n"/>
-      <c r="J193" s="4" t="n"/>
-      <c r="K193" s="4" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="18" t="inlineStr">
+      <c r="B192" s="4" t="n"/>
+      <c r="C192" s="4" t="n"/>
+      <c r="D192" s="4" t="n"/>
+      <c r="E192" s="4" t="n"/>
+      <c r="F192" s="4" t="n"/>
+      <c r="G192" s="4" t="n"/>
+      <c r="H192" s="4" t="n"/>
+      <c r="I192" s="4" t="n"/>
+      <c r="J192" s="4" t="n"/>
+      <c r="K192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="19" customHeight="1">
-      <c r="A196" s="3" t="inlineStr">
+    <row r="195" ht="19" customHeight="1">
+      <c r="A195" s="3" t="inlineStr">
         <is>
           <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 58억      오늘 2026-10-30  vs  5일전 2026-10-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B196" s="4" t="n"/>
-      <c r="C196" s="4" t="n"/>
-      <c r="D196" s="4" t="n"/>
-      <c r="E196" s="4" t="n"/>
-      <c r="F196" s="4" t="n"/>
-      <c r="G196" s="4" t="n"/>
-      <c r="H196" s="4" t="n"/>
-      <c r="I196" s="4" t="n"/>
-      <c r="J196" s="4" t="n"/>
-      <c r="K196" s="4" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="18" t="inlineStr">
+      <c r="B195" s="4" t="n"/>
+      <c r="C195" s="4" t="n"/>
+      <c r="D195" s="4" t="n"/>
+      <c r="E195" s="4" t="n"/>
+      <c r="F195" s="4" t="n"/>
+      <c r="G195" s="4" t="n"/>
+      <c r="H195" s="4" t="n"/>
+      <c r="I195" s="4" t="n"/>
+      <c r="J195" s="4" t="n"/>
+      <c r="K195" s="4" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="20" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="G185:K185"/>
+  <mergeCells count="55">
+    <mergeCell ref="A143:K143"/>
     <mergeCell ref="A73:E73"/>
     <mergeCell ref="A64:E64"/>
     <mergeCell ref="A82:E82"/>
     <mergeCell ref="G117:K117"/>
-    <mergeCell ref="A142:K142"/>
-    <mergeCell ref="A182:K182"/>
-    <mergeCell ref="G151:K151"/>
-    <mergeCell ref="A178:K178"/>
-    <mergeCell ref="A191:K191"/>
+    <mergeCell ref="A169:E169"/>
+    <mergeCell ref="G169:K169"/>
     <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A138:K138"/>
-    <mergeCell ref="G145:K145"/>
-    <mergeCell ref="A169:K169"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A94:K94"/>
-    <mergeCell ref="G170:K170"/>
-    <mergeCell ref="A197:K197"/>
+    <mergeCell ref="A168:K168"/>
     <mergeCell ref="G82:K82"/>
     <mergeCell ref="G101:K101"/>
     <mergeCell ref="A196:K196"/>
     <mergeCell ref="A137:K137"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="G37:K37"/>
+    <mergeCell ref="A177:K177"/>
+    <mergeCell ref="A183:K183"/>
+    <mergeCell ref="G184:K184"/>
     <mergeCell ref="A193:K193"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="G18:K18"/>
-    <mergeCell ref="A145:E145"/>
+    <mergeCell ref="A189:K189"/>
+    <mergeCell ref="A136:K136"/>
+    <mergeCell ref="A192:K192"/>
+    <mergeCell ref="A149:K149"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A139:K139"/>
+    <mergeCell ref="A179:K179"/>
+    <mergeCell ref="A195:K195"/>
     <mergeCell ref="G95:K95"/>
-    <mergeCell ref="A151:E151"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A185:E185"/>
-    <mergeCell ref="A194:K194"/>
     <mergeCell ref="A116:K116"/>
+    <mergeCell ref="A150:E150"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="G73:K73"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A144:K144"/>
+    <mergeCell ref="A141:K141"/>
     <mergeCell ref="G64:K64"/>
-    <mergeCell ref="A150:K150"/>
-    <mergeCell ref="A135:K135"/>
-    <mergeCell ref="A184:K184"/>
+    <mergeCell ref="A144:E144"/>
+    <mergeCell ref="A181:K181"/>
+    <mergeCell ref="A184:E184"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A100:K100"/>
-    <mergeCell ref="A140:K140"/>
+    <mergeCell ref="G144:K144"/>
     <mergeCell ref="A72:K72"/>
     <mergeCell ref="A134:K134"/>
-    <mergeCell ref="A180:K180"/>
     <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="A190:K190"/>
     <mergeCell ref="A63:K63"/>
-    <mergeCell ref="A190:K190"/>
     <mergeCell ref="A117:E117"/>
+    <mergeCell ref="G150:K150"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
